--- a/data/vessels/2026-10-30.xlsx
+++ b/data/vessels/2026-10-30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="469186" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74B8B6FB-7423-4482-9962-7F947DBF643C}"/>
+  <xr:revisionPtr revIDLastSave="469850" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56584DAD-5126-4542-824F-AB2F59692099}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="211">
   <si>
     <t>Harbor</t>
   </si>
@@ -176,25 +176,55 @@
     <t>WST</t>
   </si>
   <si>
-    <t>MATSON LANAI</t>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>MATSON ANCHORAGE</t>
   </si>
   <si>
     <t>Matson</t>
   </si>
   <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON ANCHORAGE</t>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MANULANI</t>
   </si>
   <si>
     <t>In transit</t>
   </si>
   <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MANULANI</t>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>Waiting 2.7 days</t>
+  </si>
+  <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639W</t>
   </si>
   <si>
     <t>PCT</t>
@@ -212,36 +242,6 @@
     <t>BEN LINE</t>
   </si>
   <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639W</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
     <t>LAVENDER ACE</t>
   </si>
   <si>
@@ -338,7 +338,7 @@
     <t>HYUNDAI FORWARD</t>
   </si>
   <si>
-    <t>PN32640W</t>
+    <t>PN32640E</t>
   </si>
   <si>
     <t>HMM</t>
@@ -425,27 +425,27 @@
     <t>MATSON KODIAK</t>
   </si>
   <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL SEATTLE</t>
+  </si>
+  <si>
+    <t>046E/046W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
     <t>EVER MOST</t>
   </si>
   <si>
     <t>011W</t>
   </si>
   <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL SEATTLE</t>
-  </si>
-  <si>
-    <t>046E/046W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
     <t>TONGALA</t>
   </si>
   <si>
@@ -476,30 +476,30 @@
     <t>Eukor</t>
   </si>
   <si>
+    <t>ONE FANTASTIC</t>
+  </si>
+  <si>
     <t>BUDAPEST EXPRESS</t>
   </si>
   <si>
     <t>641E/644W</t>
   </si>
   <si>
-    <t>ONE FANTASTIC</t>
-  </si>
-  <si>
     <t>LOTUS A</t>
   </si>
   <si>
     <t>CPN080S19</t>
   </si>
   <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
     <t>SUPREME ACE</t>
   </si>
   <si>
     <t>105A</t>
   </si>
   <si>
-    <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
     <t>MSC YUKTA X</t>
   </si>
   <si>
@@ -557,13 +557,16 @@
     <t>OOCL OAKLAND</t>
   </si>
   <si>
+    <t>145E</t>
+  </si>
+  <si>
     <t>RJ PFEIFFER</t>
   </si>
   <si>
     <t>YM MANDATE</t>
   </si>
   <si>
-    <t>606E</t>
+    <t>PN12643W</t>
   </si>
   <si>
     <t>OTELLO</t>
@@ -581,24 +584,24 @@
     <t>CMA CGM ARKANSAS</t>
   </si>
   <si>
+    <t>WISDOM ACE</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>THEBEN</t>
+  </si>
+  <si>
+    <t>ED617</t>
+  </si>
+  <si>
     <t>GLORIOUS ACE</t>
   </si>
   <si>
     <t>113A</t>
   </si>
   <si>
-    <t>WISDOM ACE</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>THEBEN</t>
-  </si>
-  <si>
-    <t>ED617</t>
-  </si>
-  <si>
     <t>EVER MAGUS</t>
   </si>
   <si>
@@ -611,18 +614,18 @@
     <t>PN32642W</t>
   </si>
   <si>
+    <t>EUPHONY ACE</t>
+  </si>
+  <si>
+    <t>166A</t>
+  </si>
+  <si>
     <t>TOURMALINE ACE</t>
   </si>
   <si>
     <t>013A</t>
   </si>
   <si>
-    <t>EUPHONY ACE</t>
-  </si>
-  <si>
-    <t>166A</t>
-  </si>
-  <si>
     <t>MAERSK SARNIA</t>
   </si>
   <si>
@@ -660,6 +663,9 @@
   </si>
   <si>
     <t>XIN ZHAN JIANG</t>
+  </si>
+  <si>
+    <t>201N</t>
   </si>
   <si>
     <t>MAERSK MAMMOTH</t>
@@ -738,10 +744,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L103" totalsRowShown="0">
-  <autoFilter ref="A1:L103" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L103">
-    <sortCondition ref="J2:J103"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L102" totalsRowShown="0">
+  <autoFilter ref="A1:L102" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L102">
+    <sortCondition ref="J2:J102"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1078,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1305,7 +1311,7 @@
         <v>46324.208333333336</v>
       </c>
       <c r="K6" s="2">
-        <v>46325.708333333336</v>
+        <v>46325.854166666664</v>
       </c>
       <c r="L6" t="s">
         <v>19</v>
@@ -1354,16 +1360,16 @@
         <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
         <v>38</v>
@@ -1372,13 +1378,13 @@
         <v>18</v>
       </c>
       <c r="J8" s="2">
-        <v>46325.0625</v>
+        <v>46325.104166666664</v>
       </c>
       <c r="K8" s="2">
-        <v>46325.708333333336</v>
+        <v>46325.916666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1389,16 +1395,16 @@
         <v>44</v>
       </c>
       <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" t="s">
         <v>47</v>
       </c>
-      <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" t="s">
         <v>38</v>
@@ -1407,13 +1413,13 @@
         <v>18</v>
       </c>
       <c r="J9" s="2">
-        <v>46325.104166666664</v>
+        <v>46325.291666666664</v>
       </c>
       <c r="K9" s="2">
-        <v>46325.916666666664</v>
+        <v>46326.125</v>
       </c>
       <c r="L9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1421,34 +1427,37 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="E10" s="1">
+        <v>26172</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J10" s="2">
-        <v>46325.291666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K10" s="2">
-        <v>46326.125</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L10" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1456,31 +1465,31 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
         <v>18</v>
       </c>
       <c r="J11" s="2">
-        <v>46325.5</v>
+        <v>46325.625</v>
       </c>
       <c r="K11" s="2">
-        <v>46327.208333333336</v>
-      </c>
-      <c r="L11" t="s">
-        <v>49</v>
+        <v>46327.75</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1488,31 +1497,31 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
         <v>18</v>
       </c>
       <c r="J12" s="2">
-        <v>46325.5</v>
+        <v>46325.625</v>
       </c>
       <c r="K12" s="2">
-        <v>46327.208333333336</v>
-      </c>
-      <c r="L12" t="s">
-        <v>49</v>
+        <v>46327.75</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1520,34 +1529,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
         <v>18</v>
       </c>
       <c r="J13" s="2">
-        <v>46325.625</v>
+        <v>46325.666666666664</v>
       </c>
       <c r="K13" s="2">
-        <v>46327.75</v>
+        <v>46327.25</v>
       </c>
       <c r="L13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1555,37 +1561,31 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" t="s">
         <v>62</v>
       </c>
       <c r="D14" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="1">
-        <v>26172</v>
+      <c r="E14" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
-      </c>
-      <c r="H14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="J14" s="2">
-        <v>46325.625</v>
+        <v>46325.666666666664</v>
       </c>
       <c r="K14" s="2">
-        <v>46326.041666666664</v>
+        <v>46327.25</v>
       </c>
       <c r="L14" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1593,16 +1593,16 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s">
         <v>42</v>
@@ -1611,51 +1611,51 @@
         <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J15" s="2">
-        <v>46325.625</v>
+        <v>46325.916666666664</v>
       </c>
       <c r="K15" s="2">
-        <v>46327.75</v>
+        <v>46326.708333333336</v>
       </c>
       <c r="L15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J16" s="2">
         <v>46325.916666666664</v>
       </c>
       <c r="K16" s="2">
-        <v>46326.708333333336</v>
+        <v>46327.083333333336</v>
       </c>
       <c r="L16" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1666,66 +1666,66 @@
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
         <v>18</v>
       </c>
       <c r="J17" s="2">
-        <v>46325.916666666664</v>
+        <v>46326.208333333336</v>
       </c>
       <c r="K17" s="2">
-        <v>46327.083333333336</v>
+        <v>46328.75</v>
       </c>
       <c r="L17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G18" t="s">
         <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J18" s="2">
-        <v>46326.625</v>
+        <v>46327.208333333336</v>
       </c>
       <c r="K18" s="2">
-        <v>46328.75</v>
+        <v>46327.791666666664</v>
       </c>
       <c r="L18" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1733,16 +1733,16 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
       </c>
       <c r="F19" t="s">
         <v>42</v>
@@ -1751,36 +1751,36 @@
         <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J19" s="2">
-        <v>46327.208333333336</v>
+        <v>46327.625</v>
       </c>
       <c r="K19" s="2">
-        <v>46327.791666666664</v>
+        <v>46331.166666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="1">
-        <v>2</v>
+        <v>83</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="F20" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s">
         <v>17</v>
@@ -1789,118 +1789,118 @@
         <v>18</v>
       </c>
       <c r="J20" s="2">
-        <v>46327.625</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K20" s="2">
-        <v>46331.166666666664</v>
+        <v>46328.75</v>
       </c>
       <c r="L20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="G21" t="s">
         <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J21" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.833333333336</v>
       </c>
       <c r="K21" s="2">
         <v>46328.75</v>
       </c>
       <c r="L21" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
         <v>17</v>
       </c>
+      <c r="H22" t="s">
+        <v>38</v>
+      </c>
       <c r="I22" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J22" s="2">
-        <v>46327.833333333336</v>
+        <v>46328.208333333336</v>
       </c>
       <c r="K22" s="2">
         <v>46328.75</v>
       </c>
       <c r="L22" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="G23" t="s">
         <v>17</v>
       </c>
-      <c r="H23" t="s">
-        <v>38</v>
-      </c>
       <c r="I23" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J23" s="2">
-        <v>46328.208333333336</v>
+        <v>46328.25</v>
       </c>
       <c r="K23" s="2">
-        <v>46328.75</v>
+        <v>46328.708333333336</v>
       </c>
       <c r="L23" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1908,110 +1908,110 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G24" t="s">
-        <v>17</v>
+        <v>66</v>
+      </c>
+      <c r="H24" t="s">
+        <v>94</v>
       </c>
       <c r="I24" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J24" s="2">
-        <v>46328.25</v>
+        <v>46329.208333333336</v>
       </c>
       <c r="K24" s="2">
-        <v>46328.708333333336</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="L24" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="I25" t="s">
         <v>18</v>
       </c>
       <c r="J25" s="2">
-        <v>46329.208333333336</v>
+        <v>46329.291666666664</v>
       </c>
       <c r="K25" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.166666666664</v>
       </c>
       <c r="L25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G26" t="s">
         <v>17</v>
       </c>
-      <c r="H26" t="s">
-        <v>38</v>
-      </c>
       <c r="I26" t="s">
         <v>18</v>
       </c>
       <c r="J26" s="2">
-        <v>46329.291666666664</v>
+        <v>46329.625</v>
       </c>
       <c r="K26" s="2">
-        <v>46331.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2019,34 +2019,34 @@
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F27" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>47</v>
+      </c>
+      <c r="H27" t="s">
+        <v>38</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
       </c>
       <c r="J27" s="2">
-        <v>46329.625</v>
+        <v>46330.104166666664</v>
       </c>
       <c r="K27" s="2">
-        <v>46331.75</v>
+        <v>46330.916666666664</v>
       </c>
       <c r="L27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2054,34 +2054,34 @@
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="G28" t="s">
-        <v>46</v>
-      </c>
-      <c r="H28" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J28" s="2">
-        <v>46330.104166666664</v>
+        <v>46330.25</v>
       </c>
       <c r="K28" s="2">
-        <v>46330.916666666664</v>
+        <v>46330.75</v>
       </c>
       <c r="L28" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2089,384 +2089,384 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F29" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="G29" t="s">
         <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J29" s="2">
         <v>46330.25</v>
       </c>
       <c r="K29" s="2">
-        <v>46330.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F30" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="I30" t="s">
         <v>18</v>
       </c>
       <c r="J30" s="2">
-        <v>46330.25</v>
+        <v>46330.625</v>
       </c>
       <c r="K30" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F31" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>55</v>
+      </c>
+      <c r="H31" t="s">
+        <v>55</v>
       </c>
       <c r="I31" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J31" s="2">
         <v>46330.625</v>
       </c>
       <c r="K31" s="2">
-        <v>46331.75</v>
+        <v>46331.041666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="F32" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="G32" t="s">
-        <v>65</v>
-      </c>
-      <c r="H32" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="J32" s="2">
-        <v>46330.625</v>
+        <v>46330.708333333336</v>
       </c>
       <c r="K32" s="2">
-        <v>46331.041666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F33" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="G33" t="s">
         <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J33" s="2">
-        <v>46330.708333333336</v>
+        <v>46330.791666666664</v>
       </c>
       <c r="K33" s="2">
         <v>46331.75</v>
       </c>
       <c r="L33" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F34" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>73</v>
+      </c>
+      <c r="H34" t="s">
+        <v>38</v>
       </c>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J34" s="2">
-        <v>46330.791666666664</v>
+        <v>46331.25</v>
       </c>
       <c r="K34" s="2">
-        <v>46331.75</v>
+        <v>46332.708333333336</v>
       </c>
       <c r="L34" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="E35" s="1">
+        <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="G35" t="s">
-        <v>73</v>
-      </c>
-      <c r="H35" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J35" s="2">
         <v>46331.25</v>
       </c>
       <c r="K35" s="2">
-        <v>46332.708333333336</v>
+        <v>46331.75</v>
       </c>
       <c r="L35" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
-      </c>
-      <c r="E36" s="1">
-        <v>11</v>
+        <v>123</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="F36" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="G36" t="s">
         <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J36" s="2">
-        <v>46331.25</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K36" s="2">
-        <v>46331.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L36" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="E37" s="1">
+        <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="G37" t="s">
         <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J37" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.833333333336</v>
       </c>
       <c r="K37" s="2">
         <v>46332.166666666664</v>
       </c>
       <c r="L37" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
-      </c>
-      <c r="E38" s="1">
-        <v>10</v>
+        <v>119</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="F38" t="s">
-        <v>122</v>
-      </c>
-      <c r="G38" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="I38" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J38" s="2">
-        <v>46331.833333333336</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K38" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L38" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F39" t="s">
-        <v>72</v>
+        <v>47</v>
+      </c>
+      <c r="G39" t="s">
+        <v>47</v>
+      </c>
+      <c r="H39" t="s">
+        <v>38</v>
       </c>
       <c r="I39" t="s">
         <v>18</v>
       </c>
       <c r="J39" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.104166666664</v>
       </c>
       <c r="K39" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.916666666664</v>
       </c>
       <c r="L39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2474,69 +2474,69 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>125</v>
+      </c>
+      <c r="E40" s="1">
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="G40" t="s">
-        <v>46</v>
-      </c>
-      <c r="H40" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J40" s="2">
-        <v>46332.104166666664</v>
+        <v>46332.208333333336</v>
       </c>
       <c r="K40" s="2">
-        <v>46332.916666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L40" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>125</v>
-      </c>
-      <c r="E41" s="1">
-        <v>10</v>
+        <v>129</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="F41" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G41" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I41" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J41" s="2">
-        <v>46332.208333333336</v>
+        <v>46332.25</v>
       </c>
       <c r="K41" s="2">
-        <v>46332.75</v>
+        <v>46333.166666666664</v>
       </c>
       <c r="L41" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2544,31 +2544,34 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>44</v>
+      </c>
+      <c r="C42" t="s">
+        <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F42" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G42" t="s">
-        <v>56</v>
+        <v>47</v>
+      </c>
+      <c r="H42" t="s">
+        <v>38</v>
       </c>
       <c r="I42" t="s">
         <v>18</v>
       </c>
       <c r="J42" s="2">
-        <v>46332.208333333336</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K42" s="2">
-        <v>46333.708333333336</v>
+        <v>46333.125</v>
       </c>
       <c r="L42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2576,66 +2579,63 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G43" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I43" t="s">
         <v>18</v>
       </c>
       <c r="J43" s="2">
-        <v>46332.208333333336</v>
+        <v>46332.5</v>
       </c>
       <c r="K43" s="2">
-        <v>46333.708333333336</v>
+        <v>46334.208333333336</v>
       </c>
       <c r="L43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="D44" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F44" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="G44" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="I44" t="s">
         <v>18</v>
       </c>
       <c r="J44" s="2">
-        <v>46332.25</v>
+        <v>46332.5</v>
       </c>
       <c r="K44" s="2">
-        <v>46333.166666666664</v>
+        <v>46334.208333333336</v>
       </c>
       <c r="L44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2643,34 +2643,34 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="F45" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G45" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H45" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="I45" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J45" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.625</v>
       </c>
       <c r="K45" s="2">
-        <v>46333.125</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L45" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2678,31 +2678,34 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>135</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="F46" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="G46" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
-        <v>65</v>
+        <v>137</v>
       </c>
       <c r="I46" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="J46" s="2">
-        <v>46332.625</v>
+        <v>46333.25</v>
       </c>
       <c r="K46" s="2">
-        <v>46333.041666666664</v>
+        <v>46333.75</v>
       </c>
       <c r="L46" t="s">
         <v>43</v>
@@ -2713,37 +2716,31 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F47" t="s">
-        <v>104</v>
-      </c>
-      <c r="G47" t="s">
-        <v>17</v>
-      </c>
-      <c r="H47" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I47" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J47" s="2">
-        <v>46333.25</v>
+        <v>46333.625</v>
       </c>
       <c r="K47" s="2">
-        <v>46333.75</v>
+        <v>46336.166666666664</v>
       </c>
       <c r="L47" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2751,31 +2748,37 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C48" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F48" t="s">
-        <v>140</v>
+        <v>104</v>
+      </c>
+      <c r="G48" t="s">
+        <v>17</v>
+      </c>
+      <c r="H48" t="s">
+        <v>137</v>
       </c>
       <c r="I48" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J48" s="2">
-        <v>46333.625</v>
+        <v>46333.791666666664</v>
       </c>
       <c r="K48" s="2">
-        <v>46336.166666666664</v>
+        <v>46334.75</v>
       </c>
       <c r="L48" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2783,31 +2786,28 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="C49" t="s">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F49" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="G49" t="s">
         <v>17</v>
       </c>
-      <c r="H49" t="s">
-        <v>137</v>
-      </c>
       <c r="I49" t="s">
         <v>31</v>
       </c>
       <c r="J49" s="2">
-        <v>46333.791666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K49" s="2">
         <v>46334.75</v>
@@ -2821,34 +2821,34 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>142</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
+      </c>
+      <c r="E50" s="1">
+        <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>144</v>
+        <v>42</v>
       </c>
       <c r="G50" t="s">
         <v>17</v>
       </c>
       <c r="I50" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J50" s="2">
-        <v>46334.25</v>
+        <v>46334.625</v>
       </c>
       <c r="K50" s="2">
-        <v>46334.75</v>
+        <v>46339.75</v>
       </c>
       <c r="L50" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2862,10 +2862,10 @@
         <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F51" t="s">
         <v>23</v>
@@ -2883,74 +2883,74 @@
         <v>46337.75</v>
       </c>
       <c r="L51" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D52" t="s">
-        <v>147</v>
-      </c>
-      <c r="E52" s="1">
-        <v>11</v>
+        <v>148</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="F52" t="s">
-        <v>42</v>
-      </c>
-      <c r="G52" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I52" t="s">
         <v>18</v>
       </c>
       <c r="J52" s="2">
-        <v>46334.625</v>
+        <v>46334.75</v>
       </c>
       <c r="K52" s="2">
-        <v>46339.75</v>
+        <v>46337.75</v>
       </c>
       <c r="L52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C53" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>148</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>37</v>
+        <v>122</v>
+      </c>
+      <c r="G53" t="s">
+        <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J53" s="2">
-        <v>46334.75</v>
+        <v>46335.25</v>
       </c>
       <c r="K53" s="2">
-        <v>46337.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L53" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2964,10 +2964,10 @@
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F54" t="s">
         <v>42</v>
@@ -2990,37 +2990,37 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="D55" t="s">
-        <v>152</v>
-      </c>
-      <c r="E55" s="1">
-        <v>1</v>
+        <v>153</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="F55" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="G55" t="s">
         <v>17</v>
       </c>
       <c r="I55" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J55" s="2">
-        <v>46335.25</v>
+        <v>46335.291666666664</v>
       </c>
       <c r="K55" s="2">
-        <v>46335.75</v>
+        <v>46337.166666666664</v>
       </c>
       <c r="L55" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3034,10 +3034,10 @@
         <v>95</v>
       </c>
       <c r="D56" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F56" t="s">
         <v>85</v>
@@ -3049,48 +3049,48 @@
         <v>18</v>
       </c>
       <c r="J56" s="2">
-        <v>46335.291666666664</v>
+        <v>46335.708333333336</v>
       </c>
       <c r="K56" s="2">
-        <v>46337.166666666664</v>
+        <v>46337.75</v>
       </c>
       <c r="L56" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>155</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="G57" t="s">
         <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J57" s="2">
-        <v>46335.708333333336</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K57" s="2">
-        <v>46337.75</v>
+        <v>46336.75</v>
       </c>
       <c r="L57" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3098,34 +3098,37 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="D58" t="s">
-        <v>152</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1</v>
+        <v>157</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F58" t="s">
-        <v>122</v>
+        <v>65</v>
       </c>
       <c r="G58" t="s">
-        <v>17</v>
+        <v>66</v>
+      </c>
+      <c r="H58" t="s">
+        <v>94</v>
       </c>
       <c r="I58" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J58" s="2">
-        <v>46335.791666666664</v>
+        <v>46336.208333333336</v>
       </c>
       <c r="K58" s="2">
-        <v>46336.75</v>
+        <v>46340.708333333336</v>
       </c>
       <c r="L58" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3133,7 +3136,7 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C59" t="s">
         <v>91</v>
@@ -3145,10 +3148,10 @@
         <v>158</v>
       </c>
       <c r="F59" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G59" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H59" t="s">
         <v>94</v>
@@ -3163,7 +3166,7 @@
         <v>46340.708333333336</v>
       </c>
       <c r="L59" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3171,37 +3174,37 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C60" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>157</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="E60" s="1">
+        <v>13</v>
       </c>
       <c r="F60" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G60" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="H60" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="I60" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J60" s="2">
-        <v>46336.208333333336</v>
+        <v>46336.25</v>
       </c>
       <c r="K60" s="2">
-        <v>46340.708333333336</v>
+        <v>46336.75</v>
       </c>
       <c r="L60" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3209,124 +3212,118 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D61" t="s">
-        <v>159</v>
-      </c>
-      <c r="E61" s="1">
-        <v>13</v>
+        <v>160</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="F61" t="s">
         <v>42</v>
       </c>
       <c r="G61" t="s">
-        <v>29</v>
-      </c>
-      <c r="H61" t="s">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="I61" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J61" s="2">
-        <v>46336.25</v>
+        <v>46336.625</v>
       </c>
       <c r="K61" s="2">
-        <v>46336.75</v>
+        <v>46338.75</v>
       </c>
       <c r="L61" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
-      </c>
-      <c r="C62" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F62" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="G62" t="s">
         <v>17</v>
       </c>
+      <c r="H62" t="s">
+        <v>38</v>
+      </c>
       <c r="I62" t="s">
         <v>18</v>
       </c>
       <c r="J62" s="2">
-        <v>46336.625</v>
+        <v>46337.25</v>
       </c>
       <c r="K62" s="2">
-        <v>46338.75</v>
+        <v>46337.75</v>
       </c>
       <c r="L62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>44</v>
+      </c>
+      <c r="C63" t="s">
+        <v>45</v>
       </c>
       <c r="D63" t="s">
-        <v>162</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>163</v>
+        <v>46</v>
       </c>
       <c r="F63" t="s">
-        <v>88</v>
-      </c>
-      <c r="G63" t="s">
-        <v>17</v>
-      </c>
-      <c r="H63" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I63" t="s">
         <v>18</v>
       </c>
       <c r="J63" s="2">
-        <v>46337.25</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K63" s="2">
-        <v>46337.75</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L63" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="D64" t="s">
-        <v>48</v>
+        <v>164</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="F64" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="I64" t="s">
         <v>18</v>
@@ -3335,42 +3332,45 @@
         <v>46337.333333333336</v>
       </c>
       <c r="K64" s="2">
-        <v>46337.833333333336</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L64" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C65" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="D65" t="s">
-        <v>164</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>85</v>
+        <v>54</v>
+      </c>
+      <c r="G65" t="s">
+        <v>55</v>
+      </c>
+      <c r="H65" t="s">
+        <v>55</v>
       </c>
       <c r="I65" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J65" s="2">
-        <v>46337.333333333336</v>
+        <v>46337.625</v>
       </c>
       <c r="K65" s="2">
-        <v>46339.333333333336</v>
+        <v>46338.041666666664</v>
       </c>
       <c r="L65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3378,34 +3378,31 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="D66" t="s">
-        <v>114</v>
+        <v>166</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="F66" t="s">
-        <v>64</v>
-      </c>
-      <c r="G66" t="s">
-        <v>65</v>
-      </c>
-      <c r="H66" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="I66" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="J66" s="2">
-        <v>46337.625</v>
+        <v>46337.913888888892</v>
       </c>
       <c r="K66" s="2">
-        <v>46338.041666666664</v>
+        <v>46341.205555555556</v>
       </c>
       <c r="L66" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3437,39 +3434,36 @@
         <v>46341.205555555556</v>
       </c>
       <c r="L67" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D68" t="s">
-        <v>166</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F68" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="I68" t="s">
         <v>18</v>
       </c>
       <c r="J68" s="2">
-        <v>46337.913888888892</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K68" s="2">
-        <v>46341.205555555556</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3477,28 +3471,31 @@
         <v>32</v>
       </c>
       <c r="B69" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="C69" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D69" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="F69" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="I69" t="s">
         <v>18</v>
       </c>
       <c r="J69" s="2">
-        <v>46338.431250000001</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K69" s="2">
-        <v>46339.472916666666</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L69" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3506,31 +3503,31 @@
         <v>32</v>
       </c>
       <c r="B70" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="C70" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="D70" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F70" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="I70" t="s">
         <v>18</v>
       </c>
       <c r="J70" s="2">
-        <v>46338.709027777775</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K70" s="2">
-        <v>46339.584027777775</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L70" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3541,16 +3538,16 @@
         <v>33</v>
       </c>
       <c r="C71" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D71" t="s">
         <v>171</v>
       </c>
-      <c r="E71" s="1">
-        <v>145</v>
+      <c r="E71" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="F71" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I71" t="s">
         <v>18</v>
@@ -3562,39 +3559,42 @@
         <v>46340.666666666664</v>
       </c>
       <c r="L71" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C72" t="s">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="D72" t="s">
-        <v>171</v>
-      </c>
-      <c r="E72" s="1">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="F72" t="s">
-        <v>133</v>
+        <v>54</v>
+      </c>
+      <c r="G72" t="s">
+        <v>55</v>
+      </c>
+      <c r="H72" t="s">
+        <v>55</v>
       </c>
       <c r="I72" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J72" s="2">
-        <v>46339.291666666664</v>
+        <v>46339.625</v>
       </c>
       <c r="K72" s="2">
-        <v>46340.666666666664</v>
+        <v>46340.041666666664</v>
       </c>
       <c r="L72" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3602,34 +3602,28 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D73" t="s">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c r="F73" t="s">
-        <v>64</v>
-      </c>
-      <c r="G73" t="s">
-        <v>65</v>
-      </c>
-      <c r="H73" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="I73" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="J73" s="2">
-        <v>46339.625</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K73" s="2">
-        <v>46340.041666666664</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L73" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3640,25 +3634,25 @@
         <v>44</v>
       </c>
       <c r="C74" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74" t="s">
+        <v>49</v>
+      </c>
+      <c r="F74" t="s">
         <v>47</v>
       </c>
-      <c r="D74" t="s">
-        <v>172</v>
-      </c>
-      <c r="F74" t="s">
-        <v>46</v>
-      </c>
       <c r="I74" t="s">
         <v>18</v>
       </c>
       <c r="J74" s="2">
-        <v>46339.704861111109</v>
+        <v>46340.416666666664</v>
       </c>
       <c r="K74" s="2">
-        <v>46340.204861111109</v>
+        <v>46340.75</v>
       </c>
       <c r="L74" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3666,28 +3660,31 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C75" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>174</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="F75" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="I75" t="s">
         <v>18</v>
       </c>
       <c r="J75" s="2">
-        <v>46340.416666666664</v>
+        <v>46341.208333333336</v>
       </c>
       <c r="K75" s="2">
-        <v>46340.75</v>
+        <v>46343.708333333336</v>
       </c>
       <c r="L75" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3695,66 +3692,66 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F76" t="s">
-        <v>16</v>
+        <v>104</v>
+      </c>
+      <c r="G76" t="s">
+        <v>17</v>
       </c>
       <c r="I76" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J76" s="2">
-        <v>46341.208333333336</v>
+        <v>46341.25</v>
       </c>
       <c r="K76" s="2">
-        <v>46343.708333333336</v>
+        <v>46341.75</v>
       </c>
       <c r="L76" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="D77" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F77" t="s">
-        <v>104</v>
-      </c>
-      <c r="G77" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="I77" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J77" s="2">
-        <v>46341.25</v>
+        <v>46341.333333333336</v>
       </c>
       <c r="K77" s="2">
-        <v>46341.75</v>
+        <v>46342.333333333336</v>
       </c>
       <c r="L77" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3762,63 +3759,66 @@
         <v>32</v>
       </c>
       <c r="B78" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="C78" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D78" t="s">
-        <v>177</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
+      </c>
+      <c r="E78" s="1">
+        <v>57</v>
       </c>
       <c r="F78" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="I78" t="s">
         <v>18</v>
       </c>
       <c r="J78" s="2">
-        <v>46341.333333333336</v>
+        <v>46341.62777777778</v>
       </c>
       <c r="K78" s="2">
-        <v>46342.333333333336</v>
+        <v>46346.00277777778</v>
       </c>
       <c r="L78" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C79" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
-      </c>
-      <c r="E79" s="1">
-        <v>57</v>
+        <v>176</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="F79" t="s">
-        <v>37</v>
+        <v>104</v>
+      </c>
+      <c r="G79" t="s">
+        <v>17</v>
       </c>
       <c r="I79" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J79" s="2">
-        <v>46341.62777777778</v>
+        <v>46341.791666666664</v>
       </c>
       <c r="K79" s="2">
-        <v>46346.00277777778</v>
+        <v>46342.75</v>
       </c>
       <c r="L79" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3832,22 +3832,25 @@
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="F80" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="G80" t="s">
         <v>17</v>
       </c>
+      <c r="H80" t="s">
+        <v>182</v>
+      </c>
       <c r="I80" t="s">
         <v>31</v>
       </c>
       <c r="J80" s="2">
-        <v>46341.791666666664</v>
+        <v>46342.25</v>
       </c>
       <c r="K80" s="2">
         <v>46342.75</v>
@@ -3867,17 +3870,20 @@
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F81" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="G81" t="s">
         <v>17</v>
       </c>
+      <c r="H81" t="s">
+        <v>182</v>
+      </c>
       <c r="I81" t="s">
         <v>31</v>
       </c>
@@ -3896,16 +3902,16 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="C82" t="s">
         <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="F82" t="s">
         <v>42</v>
@@ -3913,9 +3919,6 @@
       <c r="G82" t="s">
         <v>17</v>
       </c>
-      <c r="H82" t="s">
-        <v>183</v>
-      </c>
       <c r="I82" t="s">
         <v>31</v>
       </c>
@@ -3934,37 +3937,28 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>77</v>
-      </c>
-      <c r="C83" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="D83" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F83" t="s">
-        <v>104</v>
-      </c>
-      <c r="G83" t="s">
-        <v>17</v>
-      </c>
-      <c r="H83" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="I83" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J83" s="2">
         <v>46342.25</v>
       </c>
       <c r="K83" s="2">
-        <v>46342.75</v>
+        <v>46344.25</v>
       </c>
       <c r="L83" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3972,28 +3966,34 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>52</v>
+        <v>39</v>
+      </c>
+      <c r="C84" t="s">
+        <v>25</v>
       </c>
       <c r="D84" t="s">
+        <v>185</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="F84" t="s">
-        <v>55</v>
+        <v>42</v>
+      </c>
+      <c r="G84" t="s">
+        <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J84" s="2">
-        <v>46342.25</v>
+        <v>46342.791666666664</v>
       </c>
       <c r="K84" s="2">
-        <v>46344.25</v>
+        <v>46343.75</v>
       </c>
       <c r="L84" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4001,34 +4001,31 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D85" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F85" t="s">
-        <v>42</v>
-      </c>
-      <c r="G85" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="I85" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J85" s="2">
-        <v>46342.791666666664</v>
+        <v>46343.208333333336</v>
       </c>
       <c r="K85" s="2">
-        <v>46343.75</v>
+        <v>46345.125</v>
       </c>
       <c r="L85" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4036,31 +4033,37 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C86" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F86" t="s">
-        <v>140</v>
+        <v>42</v>
+      </c>
+      <c r="G86" t="s">
+        <v>17</v>
+      </c>
+      <c r="H86" t="s">
+        <v>38</v>
       </c>
       <c r="I86" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J86" s="2">
-        <v>46343.208333333336</v>
+        <v>46343.25</v>
       </c>
       <c r="K86" s="2">
-        <v>46345.125</v>
+        <v>46343.75</v>
       </c>
       <c r="L86" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4074,10 +4077,10 @@
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F87" t="s">
         <v>42</v>
@@ -4103,37 +4106,31 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D88" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F88" t="s">
-        <v>42</v>
-      </c>
-      <c r="G88" t="s">
-        <v>17</v>
-      </c>
-      <c r="H88" t="s">
-        <v>38</v>
+        <v>197</v>
       </c>
       <c r="I88" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J88" s="2">
-        <v>46343.25</v>
+        <v>46343.3125</v>
       </c>
       <c r="K88" s="2">
-        <v>46343.75</v>
+        <v>46346.604166666664</v>
       </c>
       <c r="L88" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4141,31 +4138,34 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C89" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D89" t="s">
+        <v>193</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="F89" t="s">
-        <v>196</v>
+        <v>42</v>
+      </c>
+      <c r="G89" t="s">
+        <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J89" s="2">
-        <v>46343.3125</v>
+        <v>46343.791666666664</v>
       </c>
       <c r="K89" s="2">
-        <v>46346.604166666664</v>
+        <v>46344.75</v>
       </c>
       <c r="L89" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4173,92 +4173,86 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C90" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="D90" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F90" t="s">
-        <v>42</v>
-      </c>
-      <c r="G90" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I90" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J90" s="2">
-        <v>46343.791666666664</v>
+        <v>46344</v>
       </c>
       <c r="K90" s="2">
-        <v>46344.75</v>
+        <v>46346</v>
       </c>
       <c r="L90" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B91" t="s">
-        <v>52</v>
-      </c>
-      <c r="C91" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="D91" t="s">
-        <v>197</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F91" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="I91" t="s">
         <v>18</v>
       </c>
       <c r="J91" s="2">
-        <v>46344</v>
+        <v>46344.083333333336</v>
       </c>
       <c r="K91" s="2">
-        <v>46346</v>
+        <v>46345.208333333336</v>
       </c>
       <c r="L91" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>33</v>
+        <v>44</v>
+      </c>
+      <c r="C92" t="s">
+        <v>45</v>
       </c>
       <c r="D92" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="F92" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="I92" t="s">
         <v>18</v>
       </c>
       <c r="J92" s="2">
-        <v>46344.083333333336</v>
+        <v>46344.291666666664</v>
       </c>
       <c r="K92" s="2">
-        <v>46345.208333333336</v>
+        <v>46344.791666666664</v>
       </c>
       <c r="L92" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4266,28 +4260,34 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C93" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>46</v>
+        <v>54</v>
+      </c>
+      <c r="G93" t="s">
+        <v>55</v>
+      </c>
+      <c r="H93" t="s">
+        <v>55</v>
       </c>
       <c r="I93" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J93" s="2">
-        <v>46344.291666666664</v>
+        <v>46344.625</v>
       </c>
       <c r="K93" s="2">
-        <v>46344.791666666664</v>
+        <v>46345.041666666664</v>
       </c>
       <c r="L93" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4295,69 +4295,66 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C94" t="s">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>114</v>
+        <v>201</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F94" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="G94" t="s">
-        <v>65</v>
-      </c>
-      <c r="H94" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="J94" s="2">
-        <v>46344.625</v>
+        <v>46345.25</v>
       </c>
       <c r="K94" s="2">
-        <v>46345.041666666664</v>
+        <v>46345.75</v>
       </c>
       <c r="L94" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B95" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="D95" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F95" t="s">
-        <v>42</v>
-      </c>
-      <c r="G95" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="I95" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J95" s="2">
-        <v>46345.25</v>
+        <v>46345.291666666664</v>
       </c>
       <c r="K95" s="2">
-        <v>46345.75</v>
+        <v>46346.166666666664</v>
       </c>
       <c r="L95" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4365,92 +4362,92 @@
         <v>32</v>
       </c>
       <c r="B96" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="C96" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="D96" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F96" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I96" t="s">
         <v>18</v>
       </c>
       <c r="J96" s="2">
-        <v>46345.291666666664</v>
+        <v>46346.23333333333</v>
       </c>
       <c r="K96" s="2">
-        <v>46346.166666666664</v>
+        <v>46347.275000000001</v>
       </c>
       <c r="L96" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C97" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="D97" t="s">
-        <v>204</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>205</v>
+        <v>46</v>
       </c>
       <c r="F97" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="I97" t="s">
         <v>18</v>
       </c>
       <c r="J97" s="2">
-        <v>46346.23333333333</v>
+        <v>46346.333333333336</v>
       </c>
       <c r="K97" s="2">
-        <v>46347.275000000001</v>
+        <v>46346.833333333336</v>
       </c>
       <c r="L97" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C98" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="D98" t="s">
-        <v>48</v>
+        <v>207</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F98" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
       </c>
       <c r="J98" s="2">
-        <v>46346.333333333336</v>
+        <v>46346.395833333336</v>
       </c>
       <c r="K98" s="2">
-        <v>46346.833333333336</v>
+        <v>46347.604166666664</v>
       </c>
       <c r="L98" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4464,10 +4461,10 @@
         <v>108</v>
       </c>
       <c r="D99" t="s">
-        <v>206</v>
-      </c>
-      <c r="E99" s="1">
-        <v>201</v>
+        <v>207</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F99" t="s">
         <v>140</v>
@@ -4482,7 +4479,7 @@
         <v>46347.604166666664</v>
       </c>
       <c r="L99" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4493,28 +4490,28 @@
         <v>33</v>
       </c>
       <c r="C100" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="D100" t="s">
-        <v>206</v>
-      </c>
-      <c r="E100" s="1">
-        <v>201</v>
+        <v>209</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="F100" t="s">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="I100" t="s">
         <v>18</v>
       </c>
       <c r="J100" s="2">
-        <v>46346.395833333336</v>
+        <v>46346.583333333336</v>
       </c>
       <c r="K100" s="2">
-        <v>46347.604166666664</v>
+        <v>46348.083333333336</v>
       </c>
       <c r="L100" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4528,13 +4525,13 @@
         <v>34</v>
       </c>
       <c r="D101" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F101" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
@@ -4546,74 +4543,42 @@
         <v>46348.083333333336</v>
       </c>
       <c r="L101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C102" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D102" t="s">
-        <v>207</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>208</v>
+        <v>53</v>
       </c>
       <c r="F102" t="s">
-        <v>196</v>
+        <v>54</v>
+      </c>
+      <c r="G102" t="s">
+        <v>55</v>
+      </c>
+      <c r="H102" t="s">
+        <v>55</v>
       </c>
       <c r="I102" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J102" s="2">
-        <v>46346.583333333336</v>
+        <v>46346.625</v>
       </c>
       <c r="K102" s="2">
-        <v>46348.083333333336</v>
+        <v>46347.041666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12">
-      <c r="A103" t="s">
-        <v>12</v>
-      </c>
-      <c r="B103" t="s">
-        <v>61</v>
-      </c>
-      <c r="C103" t="s">
-        <v>62</v>
-      </c>
-      <c r="D103" t="s">
-        <v>63</v>
-      </c>
-      <c r="F103" t="s">
-        <v>64</v>
-      </c>
-      <c r="G103" t="s">
-        <v>65</v>
-      </c>
-      <c r="H103" t="s">
-        <v>65</v>
-      </c>
-      <c r="I103" t="s">
-        <v>66</v>
-      </c>
-      <c r="J103" s="2">
-        <v>46346.625</v>
-      </c>
-      <c r="K103" s="2">
-        <v>46347.041666666664</v>
-      </c>
-      <c r="L103" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4625,14 +4590,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4641,7 +4598,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4779,24 +4736,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
--- a/data/vessels/2026-10-30.xlsx
+++ b/data/vessels/2026-10-30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="469850" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56584DAD-5126-4542-824F-AB2F59692099}"/>
+  <xr:revisionPtr revIDLastSave="470379" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF28954D-A0AA-434A-87CC-755FA5FB5F65}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="201">
   <si>
     <t>Harbor</t>
   </si>
@@ -83,589 +83,559 @@
     <t>Husky</t>
   </si>
   <si>
+    <t>WC4/TP5</t>
+  </si>
+  <si>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E/643W</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
+    <t>Norton Lilly International</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>At berth</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MANULANI</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>Waiting 2.9 days</t>
+  </si>
+  <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639W</t>
+  </si>
+  <si>
+    <t>ONE</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>EVER MODE</t>
+  </si>
+  <si>
+    <t>010W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>Ad Hoc</t>
+  </si>
+  <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>EB Service 2</t>
+  </si>
+  <si>
+    <t>NADI CHIEF</t>
+  </si>
+  <si>
+    <t>015E/016W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CYPRESS</t>
+  </si>
+  <si>
+    <t>CPN06/CPN07</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>SWIFT ACE</t>
+  </si>
+  <si>
+    <t>152A</t>
+  </si>
+  <si>
     <t>FP2</t>
   </si>
   <si>
-    <t>YM TUTORIAL</t>
+    <t>ONE SYNERGY</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC643R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>SM TIANJIN</t>
+  </si>
+  <si>
+    <t>2606E/2606W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>EUROPEAN HIGHWAY</t>
+  </si>
+  <si>
+    <t>285A</t>
+  </si>
+  <si>
+    <t>TPN</t>
+  </si>
+  <si>
+    <t>EVER SMILE</t>
+  </si>
+  <si>
+    <t>136W</t>
+  </si>
+  <si>
+    <t>Everport Terminal Services</t>
+  </si>
+  <si>
+    <t>MSC IVANA</t>
+  </si>
+  <si>
+    <t>UK642R</t>
+  </si>
+  <si>
+    <t>HYUNDAI FORWARD</t>
+  </si>
+  <si>
+    <t>PN32640E</t>
+  </si>
+  <si>
+    <t>HMM</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>MORNING LUCY</t>
+  </si>
+  <si>
+    <t>A6179</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>ONE MAJESTY</t>
+  </si>
+  <si>
+    <t>PN12641W</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>COSCO SANTOS</t>
+  </si>
+  <si>
+    <t>102N/102E</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>MSC FLORA</t>
+  </si>
+  <si>
+    <t>MC644R</t>
+  </si>
+  <si>
+    <t>KW665</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD COLUMBIA</t>
+  </si>
+  <si>
+    <t>156E/157W</t>
+  </si>
+  <si>
+    <t>GLOVIS TRUST</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
+    <t>MSC SABRINA</t>
+  </si>
+  <si>
+    <t>MC645R</t>
+  </si>
+  <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
+    <t>156E</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL SEATTLE</t>
+  </si>
+  <si>
+    <t>046E/046W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>EVER MOST</t>
+  </si>
+  <si>
+    <t>011W</t>
+  </si>
+  <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>A6178</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
+    <t>CORNEILLE</t>
+  </si>
+  <si>
+    <t>PN12642E</t>
+  </si>
+  <si>
+    <t>Not Specified</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>ONE FANTASTIC</t>
+  </si>
+  <si>
+    <t>BUDAPEST EXPRESS</t>
+  </si>
+  <si>
+    <t>641E/644W</t>
+  </si>
+  <si>
+    <t>LOTUS A</t>
+  </si>
+  <si>
+    <t>CPN080S19</t>
+  </si>
+  <si>
+    <t>SUPREME ACE</t>
+  </si>
+  <si>
+    <t>105A</t>
+  </si>
+  <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>MSC YUKTA X</t>
+  </si>
+  <si>
+    <t>UK644R</t>
+  </si>
+  <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK643R</t>
+  </si>
+  <si>
+    <t>EVER STRONG</t>
+  </si>
+  <si>
+    <t>134W</t>
+  </si>
+  <si>
+    <t>NOCC ADRIATIC</t>
+  </si>
+  <si>
+    <t>A6177</t>
+  </si>
+  <si>
+    <t>Eukor</t>
+  </si>
+  <si>
+    <t>PAVO LEADER</t>
+  </si>
+  <si>
+    <t>ONE MODERN</t>
+  </si>
+  <si>
+    <t>PN32641W</t>
+  </si>
+  <si>
+    <t>SM MUMBAI</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>MATSON ANCHORAGE</t>
+  </si>
+  <si>
+    <t>MSC LISBON IX</t>
+  </si>
+  <si>
+    <t>UK641A</t>
+  </si>
+  <si>
+    <t>SANTA RITA</t>
+  </si>
+  <si>
+    <t>645W</t>
+  </si>
+  <si>
+    <t>LAUTOKA CHIEF</t>
+  </si>
+  <si>
+    <t>MSC HORTENSE</t>
+  </si>
+  <si>
+    <t>MC639A</t>
+  </si>
+  <si>
+    <t>OOCL OAKLAND</t>
+  </si>
+  <si>
+    <t>145E</t>
+  </si>
+  <si>
+    <t>RJ PFEIFFER</t>
+  </si>
+  <si>
+    <t>YM MANDATE</t>
+  </si>
+  <si>
+    <t>PN12643W</t>
   </si>
   <si>
     <t>Yang Ming</t>
   </si>
   <si>
-    <t>Norton Lilly International</t>
-  </si>
-  <si>
-    <t>Container</t>
-  </si>
-  <si>
-    <t>At berth</t>
-  </si>
-  <si>
-    <t>WC4/TP5</t>
-  </si>
-  <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E/643W</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>Ad Hoc</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>T18</t>
+    <t>MSC DESIREE</t>
+  </si>
+  <si>
+    <t>UK642A</t>
+  </si>
+  <si>
+    <t>CMA CGM ARKANSAS</t>
+  </si>
+  <si>
+    <t>WISDOM ACE</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>THEBEN</t>
+  </si>
+  <si>
+    <t>ED617</t>
+  </si>
+  <si>
+    <t>GLORIOUS ACE</t>
+  </si>
+  <si>
+    <t>113A</t>
+  </si>
+  <si>
+    <t>EVER MAGUS</t>
+  </si>
+  <si>
+    <t>1476-009E</t>
+  </si>
+  <si>
+    <t>HMM VANCOUVER</t>
+  </si>
+  <si>
+    <t>PN32642W</t>
+  </si>
+  <si>
+    <t>OTELLO</t>
+  </si>
+  <si>
+    <t>A6193</t>
+  </si>
+  <si>
+    <t>EUPHONY ACE</t>
+  </si>
+  <si>
+    <t>166A</t>
+  </si>
+  <si>
+    <t>TOURMALINE ACE</t>
+  </si>
+  <si>
+    <t>013A</t>
+  </si>
+  <si>
+    <t>MAERSK SARNIA</t>
+  </si>
+  <si>
+    <t>643E</t>
+  </si>
+  <si>
+    <t>Maersk</t>
+  </si>
+  <si>
+    <t>EVER SUMMIT</t>
+  </si>
+  <si>
+    <t>498-133E</t>
+  </si>
+  <si>
+    <t>SM SEOUL</t>
+  </si>
+  <si>
+    <t>BERGAMOT ACE</t>
+  </si>
+  <si>
+    <t>159A</t>
+  </si>
+  <si>
+    <t>MSC ELISABETTA</t>
+  </si>
+  <si>
+    <t>MC640A</t>
+  </si>
+  <si>
+    <t>WESTWOOD OLYMPIA</t>
+  </si>
+  <si>
+    <t>140E</t>
+  </si>
+  <si>
+    <t>XIN ZHAN JIANG</t>
+  </si>
+  <si>
+    <t>201N</t>
   </si>
   <si>
     <t>Oceania</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>0Y1N2/0T1N3</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
-    <t>ONE</t>
-  </si>
-  <si>
-    <t>Not available</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON ANCHORAGE</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MANULANI</t>
-  </si>
-  <si>
-    <t>In transit</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>Waiting 2.7 days</t>
-  </si>
-  <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639W</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>EVER MODE</t>
-  </si>
-  <si>
-    <t>010W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
-    <t>EB Service 2</t>
-  </si>
-  <si>
-    <t>NADI CHIEF</t>
-  </si>
-  <si>
-    <t>015E/016W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CYPRESS</t>
-  </si>
-  <si>
-    <t>CPN06/CPN07</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>SWIFT ACE</t>
-  </si>
-  <si>
-    <t>152A</t>
-  </si>
-  <si>
-    <t>ONE SYNERGY</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC643R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>SM TIANJIN</t>
-  </si>
-  <si>
-    <t>2606E/2606W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>EUROPEAN HIGHWAY</t>
-  </si>
-  <si>
-    <t>285A</t>
-  </si>
-  <si>
-    <t>TPN</t>
-  </si>
-  <si>
-    <t>EVER SMILE</t>
-  </si>
-  <si>
-    <t>136W</t>
-  </si>
-  <si>
-    <t>Everport Terminal Services</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>MSC IVANA</t>
-  </si>
-  <si>
-    <t>UK642R</t>
-  </si>
-  <si>
-    <t>HYUNDAI FORWARD</t>
-  </si>
-  <si>
-    <t>PN32640E</t>
-  </si>
-  <si>
-    <t>HMM</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>MORNING LUCY</t>
-  </si>
-  <si>
-    <t>A6179</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>ONE MAJESTY</t>
-  </si>
-  <si>
-    <t>PN12641W</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>COSCO SANTOS</t>
-  </si>
-  <si>
-    <t>102N/102E</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>MSC FLORA</t>
-  </si>
-  <si>
-    <t>MC644R</t>
-  </si>
-  <si>
-    <t>KW665</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD COLUMBIA</t>
-  </si>
-  <si>
-    <t>156E/157W</t>
-  </si>
-  <si>
-    <t>GLOVIS TRUST</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>MSC SABRINA</t>
-  </si>
-  <si>
-    <t>MC645R</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>156E</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL SEATTLE</t>
-  </si>
-  <si>
-    <t>046E/046W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>EVER MOST</t>
-  </si>
-  <si>
-    <t>011W</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>A6178</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
-    <t>CORNEILLE</t>
-  </si>
-  <si>
-    <t>PN12642E</t>
-  </si>
-  <si>
-    <t>Not Specified</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>NOCC ADRIATIC</t>
-  </si>
-  <si>
-    <t>A6177</t>
-  </si>
-  <si>
-    <t>Eukor</t>
-  </si>
-  <si>
-    <t>ONE FANTASTIC</t>
-  </si>
-  <si>
-    <t>BUDAPEST EXPRESS</t>
-  </si>
-  <si>
-    <t>641E/644W</t>
-  </si>
-  <si>
-    <t>LOTUS A</t>
-  </si>
-  <si>
-    <t>CPN080S19</t>
-  </si>
-  <si>
-    <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>SUPREME ACE</t>
-  </si>
-  <si>
-    <t>105A</t>
-  </si>
-  <si>
-    <t>MSC YUKTA X</t>
-  </si>
-  <si>
-    <t>UK644R</t>
-  </si>
-  <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK643R</t>
-  </si>
-  <si>
-    <t>EVER STRONG</t>
-  </si>
-  <si>
-    <t>134W</t>
-  </si>
-  <si>
-    <t>PAVO LEADER</t>
-  </si>
-  <si>
-    <t>ONE MODERN</t>
-  </si>
-  <si>
-    <t>PN32641W</t>
-  </si>
-  <si>
-    <t>SM MUMBAI</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>MSC LISBON IX</t>
-  </si>
-  <si>
-    <t>UK641A</t>
-  </si>
-  <si>
-    <t>SANTA RITA</t>
-  </si>
-  <si>
-    <t>645W</t>
-  </si>
-  <si>
-    <t>LAUTOKA CHIEF</t>
-  </si>
-  <si>
-    <t>MSC HORTENSE</t>
-  </si>
-  <si>
-    <t>MC639A</t>
-  </si>
-  <si>
-    <t>OOCL OAKLAND</t>
-  </si>
-  <si>
-    <t>145E</t>
-  </si>
-  <si>
-    <t>RJ PFEIFFER</t>
-  </si>
-  <si>
-    <t>YM MANDATE</t>
-  </si>
-  <si>
-    <t>PN12643W</t>
-  </si>
-  <si>
-    <t>OTELLO</t>
-  </si>
-  <si>
-    <t>A6193</t>
-  </si>
-  <si>
-    <t>MSC DESIREE</t>
-  </si>
-  <si>
-    <t>UK642A</t>
-  </si>
-  <si>
-    <t>CMA CGM ARKANSAS</t>
-  </si>
-  <si>
-    <t>WISDOM ACE</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>THEBEN</t>
-  </si>
-  <si>
-    <t>ED617</t>
-  </si>
-  <si>
-    <t>GLORIOUS ACE</t>
-  </si>
-  <si>
-    <t>113A</t>
-  </si>
-  <si>
-    <t>EVER MAGUS</t>
-  </si>
-  <si>
-    <t>1476-009E</t>
-  </si>
-  <si>
-    <t>HMM VANCOUVER</t>
-  </si>
-  <si>
-    <t>PN32642W</t>
-  </si>
-  <si>
-    <t>EUPHONY ACE</t>
-  </si>
-  <si>
-    <t>166A</t>
-  </si>
-  <si>
-    <t>TOURMALINE ACE</t>
-  </si>
-  <si>
-    <t>013A</t>
-  </si>
-  <si>
-    <t>MAERSK SARNIA</t>
-  </si>
-  <si>
-    <t>643E</t>
-  </si>
-  <si>
-    <t>Maersk</t>
-  </si>
-  <si>
-    <t>EVER SUMMIT</t>
-  </si>
-  <si>
-    <t>498-133E</t>
-  </si>
-  <si>
-    <t>SM SEOUL</t>
-  </si>
-  <si>
-    <t>BERGAMOT ACE</t>
-  </si>
-  <si>
-    <t>159A</t>
-  </si>
-  <si>
-    <t>MSC ELISABETTA</t>
-  </si>
-  <si>
-    <t>MC640A</t>
-  </si>
-  <si>
-    <t>WESTWOOD OLYMPIA</t>
-  </si>
-  <si>
-    <t>140E</t>
-  </si>
-  <si>
-    <t>XIN ZHAN JIANG</t>
-  </si>
-  <si>
-    <t>201N</t>
   </si>
   <si>
     <t>MAERSK MAMMOTH</t>
@@ -744,10 +714,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L102" totalsRowShown="0">
-  <autoFilter ref="A1:L102" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L102">
-    <sortCondition ref="J2:J102"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L98" totalsRowShown="0">
+  <autoFilter ref="A1:L98" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L98">
+    <sortCondition ref="J2:J98"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1084,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1149,26 +1119,26 @@
       <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1">
-        <v>21</v>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="2">
-        <v>46319.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K2" s="2">
-        <v>46325.75</v>
+        <v>46329.75</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1179,22 +1149,22 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="2">
         <v>46322.625</v>
@@ -1203,7 +1173,7 @@
         <v>46329.75</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1211,34 +1181,34 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="2">
-        <v>46322.625</v>
+        <v>46325.291666666664</v>
       </c>
       <c r="K4" s="2">
-        <v>46329.75</v>
+        <v>46326.125</v>
       </c>
       <c r="L4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1246,75 +1216,69 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="E5" s="1">
+        <v>26172</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J5" s="2">
-        <v>46322.791666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K5" s="2">
-        <v>46325.770833333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="2">
-        <v>46324.208333333336</v>
+        <v>46325.625</v>
       </c>
       <c r="K6" s="2">
-        <v>46325.854166666664</v>
-      </c>
-      <c r="L6" t="s">
-        <v>19</v>
+        <v>46327.75</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1322,34 +1286,31 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J7" s="2">
-        <v>46324.875</v>
+        <v>46325.625</v>
       </c>
       <c r="K7" s="2">
-        <v>46325.791666666664</v>
-      </c>
-      <c r="L7" t="s">
-        <v>43</v>
+        <v>46327.75</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1357,34 +1318,31 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>40</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="2">
-        <v>46325.104166666664</v>
+        <v>46325.666666666664</v>
       </c>
       <c r="K8" s="2">
-        <v>46325.916666666664</v>
+        <v>46327.25</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1392,34 +1350,31 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>40</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" s="2">
-        <v>46325.291666666664</v>
+        <v>46325.666666666664</v>
       </c>
       <c r="K9" s="2">
-        <v>46326.125</v>
+        <v>46327.25</v>
       </c>
       <c r="L9" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1427,101 +1382,104 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="1">
-        <v>26172</v>
+        <v>46</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J10" s="2">
-        <v>46325.625</v>
+        <v>46325.916666666664</v>
       </c>
       <c r="K10" s="2">
-        <v>46326.041666666664</v>
+        <v>46326.708333333336</v>
       </c>
       <c r="L10" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="2">
-        <v>46325.625</v>
+        <v>46325.916666666664</v>
       </c>
       <c r="K11" s="2">
-        <v>46327.75</v>
+        <v>46327.083333333336</v>
+      </c>
+      <c r="L11" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
         <v>58</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" s="2">
-        <v>46325.625</v>
+        <v>46326.208333333336</v>
       </c>
       <c r="K12" s="2">
-        <v>46327.75</v>
+        <v>46328.75</v>
+      </c>
+      <c r="L12" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1529,31 +1487,34 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
         <v>62</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J13" s="2">
-        <v>46325.666666666664</v>
+        <v>46327.208333333336</v>
       </c>
       <c r="K13" s="2">
-        <v>46327.25</v>
+        <v>46327.791666666664</v>
       </c>
       <c r="L13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1561,31 +1522,34 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="G14" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="2">
-        <v>46325.666666666664</v>
+        <v>46327.625</v>
       </c>
       <c r="K14" s="2">
-        <v>46327.25</v>
+        <v>46334.333333333336</v>
       </c>
       <c r="L14" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1593,139 +1557,139 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J15" s="2">
-        <v>46325.916666666664</v>
+        <v>46327.625</v>
       </c>
       <c r="K15" s="2">
-        <v>46326.708333333336</v>
+        <v>46334.333333333336</v>
       </c>
       <c r="L15" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" t="s">
-        <v>72</v>
-      </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="2">
-        <v>46325.916666666664</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K16" s="2">
-        <v>46327.083333333336</v>
+        <v>46328.75</v>
       </c>
       <c r="L16" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J17" s="2">
-        <v>46326.208333333336</v>
+        <v>46327.833333333336</v>
       </c>
       <c r="K17" s="2">
         <v>46328.75</v>
       </c>
       <c r="L17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" t="s">
         <v>25</v>
       </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" t="s">
-        <v>17</v>
-      </c>
       <c r="I18" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J18" s="2">
-        <v>46327.208333333336</v>
+        <v>46328.208333333336</v>
       </c>
       <c r="K18" s="2">
-        <v>46327.791666666664</v>
+        <v>46328.75</v>
       </c>
       <c r="L18" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1733,139 +1697,145 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" s="1">
-        <v>2</v>
+        <v>74</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J19" s="2">
-        <v>46327.625</v>
+        <v>46328.25</v>
       </c>
       <c r="K19" s="2">
-        <v>46331.166666666664</v>
+        <v>46328.708333333336</v>
       </c>
       <c r="L19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>43</v>
+      </c>
+      <c r="H20" t="s">
+        <v>79</v>
       </c>
       <c r="I20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.208333333336</v>
       </c>
       <c r="K20" s="2">
-        <v>46328.75</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="L20" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" t="s">
         <v>25</v>
       </c>
-      <c r="D21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" t="s">
-        <v>17</v>
-      </c>
       <c r="I21" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J21" s="2">
-        <v>46327.833333333336</v>
+        <v>46329.291666666664</v>
       </c>
       <c r="K21" s="2">
-        <v>46328.75</v>
+        <v>46331.166666666664</v>
       </c>
       <c r="L21" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" s="2">
-        <v>46328.208333333336</v>
+        <v>46329.625</v>
       </c>
       <c r="K22" s="2">
-        <v>46328.75</v>
+        <v>46331.75</v>
       </c>
       <c r="L22" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1873,34 +1843,34 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" t="s">
         <v>25</v>
       </c>
-      <c r="D23" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" t="s">
-        <v>17</v>
-      </c>
       <c r="I23" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J23" s="2">
-        <v>46328.25</v>
+        <v>46330.104166666664</v>
       </c>
       <c r="K23" s="2">
-        <v>46328.708333333336</v>
+        <v>46330.916666666664</v>
       </c>
       <c r="L23" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1908,110 +1878,104 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
-      </c>
-      <c r="H24" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J24" s="2">
-        <v>46329.208333333336</v>
+        <v>46330.25</v>
       </c>
       <c r="K24" s="2">
-        <v>46331.791666666664</v>
+        <v>46330.75</v>
       </c>
       <c r="L24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" s="2">
-        <v>46329.291666666664</v>
+        <v>46330.25</v>
       </c>
       <c r="K25" s="2">
-        <v>46331.166666666664</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L25" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F26" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="I26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J26" s="2">
-        <v>46329.625</v>
+        <v>46330.625</v>
       </c>
       <c r="K26" s="2">
         <v>46331.75</v>
       </c>
       <c r="L26" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2019,69 +1983,69 @@
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F27" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H27" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I27" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J27" s="2">
-        <v>46330.104166666664</v>
+        <v>46330.625</v>
       </c>
       <c r="K27" s="2">
-        <v>46330.916666666664</v>
+        <v>46331.041666666664</v>
       </c>
       <c r="L27" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F28" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J28" s="2">
-        <v>46330.25</v>
+        <v>46330.708333333336</v>
       </c>
       <c r="K28" s="2">
-        <v>46330.75</v>
+        <v>46331.75</v>
       </c>
       <c r="L28" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2089,69 +2053,72 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J29" s="2">
-        <v>46330.25</v>
+        <v>46330.791666666664</v>
       </c>
       <c r="K29" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F30" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>56</v>
+      </c>
+      <c r="H30" t="s">
+        <v>25</v>
       </c>
       <c r="I30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J30" s="2">
-        <v>46330.625</v>
+        <v>46331.25</v>
       </c>
       <c r="K30" s="2">
-        <v>46331.75</v>
+        <v>46332.708333333336</v>
       </c>
       <c r="L30" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2159,69 +2126,69 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>114</v>
+        <v>106</v>
+      </c>
+      <c r="E31" s="1">
+        <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="G31" t="s">
-        <v>55</v>
-      </c>
-      <c r="H31" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J31" s="2">
-        <v>46330.625</v>
+        <v>46331.270833333336</v>
       </c>
       <c r="K31" s="2">
-        <v>46331.041666666664</v>
+        <v>46331.729166666664</v>
       </c>
       <c r="L31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F32" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="G32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J32" s="2">
-        <v>46330.708333333336</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K32" s="2">
-        <v>46331.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L32" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2229,72 +2196,66 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
+      </c>
+      <c r="E33" s="1">
+        <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J33" s="2">
-        <v>46330.791666666664</v>
+        <v>46331.833333333336</v>
       </c>
       <c r="K33" s="2">
-        <v>46331.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L33" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F34" t="s">
-        <v>72</v>
-      </c>
-      <c r="G34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H34" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" s="2">
-        <v>46331.25</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K34" s="2">
-        <v>46332.708333333336</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L34" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2302,136 +2263,139 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" t="s">
         <v>25</v>
       </c>
-      <c r="D35" t="s">
-        <v>121</v>
-      </c>
-      <c r="E35" s="1">
-        <v>11</v>
-      </c>
-      <c r="F35" t="s">
-        <v>122</v>
-      </c>
-      <c r="G35" t="s">
-        <v>17</v>
-      </c>
       <c r="I35" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J35" s="2">
-        <v>46331.25</v>
+        <v>46332.104166666664</v>
       </c>
       <c r="K35" s="2">
-        <v>46331.75</v>
+        <v>46332.916666666664</v>
       </c>
       <c r="L35" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>124</v>
+        <v>110</v>
+      </c>
+      <c r="E36" s="1">
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J36" s="2">
-        <v>46331.291666666664</v>
+        <v>46332.208333333336</v>
       </c>
       <c r="K36" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
-      </c>
-      <c r="E37" s="1">
-        <v>10</v>
+        <v>114</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="F37" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="I37" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J37" s="2">
-        <v>46331.833333333336</v>
+        <v>46332.25</v>
       </c>
       <c r="K37" s="2">
-        <v>46332.166666666664</v>
+        <v>46333.166666666664</v>
       </c>
       <c r="L37" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" t="s">
         <v>118</v>
       </c>
-      <c r="D38" t="s">
-        <v>119</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="F38" t="s">
-        <v>72</v>
+        <v>24</v>
+      </c>
+      <c r="G38" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" t="s">
+        <v>25</v>
       </c>
       <c r="I38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J38" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K38" s="2">
-        <v>46332.597916666666</v>
+        <v>46333.125</v>
       </c>
       <c r="L38" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2439,34 +2403,31 @@
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>119</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="F39" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G39" t="s">
-        <v>47</v>
-      </c>
-      <c r="H39" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J39" s="2">
-        <v>46332.104166666664</v>
+        <v>46332.5</v>
       </c>
       <c r="K39" s="2">
-        <v>46332.916666666664</v>
+        <v>46334.208333333336</v>
       </c>
       <c r="L39" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2476,67 +2437,64 @@
       <c r="B40" t="s">
         <v>39</v>
       </c>
-      <c r="C40" t="s">
-        <v>25</v>
-      </c>
       <c r="D40" t="s">
-        <v>125</v>
-      </c>
-      <c r="E40" s="1">
-        <v>10</v>
+        <v>119</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="F40" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="G40" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I40" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J40" s="2">
-        <v>46332.208333333336</v>
+        <v>46332.5</v>
       </c>
       <c r="K40" s="2">
-        <v>46332.75</v>
+        <v>46334.208333333336</v>
       </c>
       <c r="L40" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H41" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" t="s">
         <v>32</v>
       </c>
-      <c r="B41" t="s">
+      <c r="J41" s="2">
+        <v>46332.625</v>
+      </c>
+      <c r="K41" s="2">
+        <v>46333.041666666664</v>
+      </c>
+      <c r="L41" t="s">
         <v>33</v>
-      </c>
-      <c r="C41" t="s">
-        <v>128</v>
-      </c>
-      <c r="D41" t="s">
-        <v>129</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F41" t="s">
-        <v>131</v>
-      </c>
-      <c r="G41" t="s">
-        <v>29</v>
-      </c>
-      <c r="I41" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="2">
-        <v>46332.25</v>
-      </c>
-      <c r="K41" s="2">
-        <v>46333.166666666664</v>
-      </c>
-      <c r="L41" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2544,34 +2502,37 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F42" t="s">
+        <v>89</v>
+      </c>
+      <c r="G42" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" t="s">
+        <v>123</v>
+      </c>
+      <c r="I42" t="s">
         <v>48</v>
       </c>
-      <c r="D42" t="s">
-        <v>132</v>
-      </c>
-      <c r="F42" t="s">
-        <v>47</v>
-      </c>
-      <c r="G42" t="s">
-        <v>47</v>
-      </c>
-      <c r="H42" t="s">
-        <v>38</v>
-      </c>
-      <c r="I42" t="s">
-        <v>18</v>
-      </c>
       <c r="J42" s="2">
-        <v>46332.291666666664</v>
+        <v>46333.25</v>
       </c>
       <c r="K42" s="2">
-        <v>46333.125</v>
+        <v>46333.75</v>
       </c>
       <c r="L42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2579,31 +2540,31 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>34</v>
+      </c>
+      <c r="C43" t="s">
+        <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="F43" t="s">
-        <v>65</v>
-      </c>
-      <c r="G43" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="I43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J43" s="2">
-        <v>46332.5</v>
+        <v>46333.625</v>
       </c>
       <c r="K43" s="2">
-        <v>46334.208333333336</v>
+        <v>46336.166666666664</v>
       </c>
       <c r="L43" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2611,31 +2572,37 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
+        <v>45</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F44" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s">
-        <v>66</v>
+        <v>18</v>
+      </c>
+      <c r="H44" t="s">
+        <v>123</v>
       </c>
       <c r="I44" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J44" s="2">
-        <v>46332.5</v>
+        <v>46333.791666666664</v>
       </c>
       <c r="K44" s="2">
-        <v>46334.208333333336</v>
+        <v>46334.75</v>
       </c>
       <c r="L44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2643,34 +2610,34 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>128</v>
+      </c>
+      <c r="E45" s="1">
+        <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G45" t="s">
-        <v>55</v>
-      </c>
-      <c r="H45" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="J45" s="2">
-        <v>46332.625</v>
+        <v>46334.625</v>
       </c>
       <c r="K45" s="2">
-        <v>46333.041666666664</v>
+        <v>46339.75</v>
       </c>
       <c r="L45" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2678,69 +2645,66 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F46" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>17</v>
-      </c>
-      <c r="H46" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J46" s="2">
-        <v>46333.25</v>
+        <v>46334.625</v>
       </c>
       <c r="K46" s="2">
-        <v>46333.75</v>
+        <v>46337.75</v>
       </c>
       <c r="L46" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F47" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="I47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J47" s="2">
-        <v>46333.625</v>
+        <v>46334.75</v>
       </c>
       <c r="K47" s="2">
-        <v>46336.166666666664</v>
+        <v>46337.75</v>
       </c>
       <c r="L47" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2748,37 +2712,34 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F48" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="G48" t="s">
-        <v>17</v>
-      </c>
-      <c r="H48" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J48" s="2">
-        <v>46333.791666666664</v>
+        <v>46335.25</v>
       </c>
       <c r="K48" s="2">
-        <v>46334.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L48" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2786,136 +2747,139 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="G49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J49" s="2">
-        <v>46334.25</v>
+        <v>46335.25</v>
       </c>
       <c r="K49" s="2">
-        <v>46334.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L49" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
-      </c>
-      <c r="E50" s="1">
-        <v>11</v>
+        <v>137</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="F50" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="G50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J50" s="2">
-        <v>46334.625</v>
+        <v>46335.291666666664</v>
       </c>
       <c r="K50" s="2">
-        <v>46339.75</v>
+        <v>46337.166666666664</v>
       </c>
       <c r="L50" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J51" s="2">
-        <v>46334.625</v>
+        <v>46335.708333333336</v>
       </c>
       <c r="K51" s="2">
         <v>46337.75</v>
       </c>
       <c r="L51" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D52" t="s">
-        <v>148</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>149</v>
+        <v>135</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>37</v>
+        <v>107</v>
+      </c>
+      <c r="G52" t="s">
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J52" s="2">
-        <v>46334.75</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K52" s="2">
-        <v>46337.75</v>
+        <v>46336.75</v>
       </c>
       <c r="L52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2926,31 +2890,34 @@
         <v>39</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D53" t="s">
-        <v>150</v>
-      </c>
-      <c r="E53" s="1">
-        <v>1</v>
+        <v>141</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="F53" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="G53" t="s">
-        <v>17</v>
+        <v>43</v>
+      </c>
+      <c r="H53" t="s">
+        <v>79</v>
       </c>
       <c r="I53" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J53" s="2">
-        <v>46335.25</v>
+        <v>46336.208333333336</v>
       </c>
       <c r="K53" s="2">
-        <v>46335.75</v>
+        <v>46340.708333333336</v>
       </c>
       <c r="L53" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2961,101 +2928,107 @@
         <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D54" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="F54" t="s">
         <v>42</v>
       </c>
       <c r="G54" t="s">
-        <v>17</v>
+        <v>43</v>
+      </c>
+      <c r="H54" t="s">
+        <v>79</v>
       </c>
       <c r="I54" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J54" s="2">
-        <v>46335.25</v>
+        <v>46336.208333333336</v>
       </c>
       <c r="K54" s="2">
-        <v>46335.75</v>
+        <v>46340.708333333336</v>
       </c>
       <c r="L54" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="D55" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F55" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="G55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J55" s="2">
-        <v>46335.291666666664</v>
+        <v>46336.25</v>
       </c>
       <c r="K55" s="2">
-        <v>46337.166666666664</v>
+        <v>46336.75</v>
       </c>
       <c r="L55" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="C56" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>155</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
+      </c>
+      <c r="E56" s="1">
+        <v>13</v>
       </c>
       <c r="F56" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="G56" t="s">
-        <v>17</v>
+        <v>117</v>
+      </c>
+      <c r="H56" t="s">
+        <v>123</v>
       </c>
       <c r="I56" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J56" s="2">
-        <v>46335.708333333336</v>
+        <v>46336.25</v>
       </c>
       <c r="K56" s="2">
-        <v>46337.75</v>
+        <v>46336.75</v>
       </c>
       <c r="L56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3063,72 +3036,69 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D57" t="s">
-        <v>150</v>
-      </c>
-      <c r="E57" s="1">
-        <v>1</v>
+        <v>147</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="F57" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="G57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J57" s="2">
-        <v>46335.791666666664</v>
+        <v>46336.625</v>
       </c>
       <c r="K57" s="2">
-        <v>46336.75</v>
+        <v>46338.75</v>
       </c>
       <c r="L57" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
-      </c>
-      <c r="C58" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="D58" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F58" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G58" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="H58" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="I58" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J58" s="2">
-        <v>46336.208333333336</v>
+        <v>46337.25</v>
       </c>
       <c r="K58" s="2">
-        <v>46340.708333333336</v>
+        <v>46337.75</v>
       </c>
       <c r="L58" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3136,75 +3106,60 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="C59" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D59" t="s">
-        <v>157</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F59" t="s">
-        <v>65</v>
-      </c>
-      <c r="G59" t="s">
-        <v>66</v>
-      </c>
-      <c r="H59" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="I59" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J59" s="2">
-        <v>46336.208333333336</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K59" s="2">
-        <v>46340.708333333336</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B60" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="D60" t="s">
-        <v>159</v>
-      </c>
-      <c r="E60" s="1">
-        <v>13</v>
+        <v>152</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="F60" t="s">
-        <v>42</v>
-      </c>
-      <c r="G60" t="s">
-        <v>29</v>
-      </c>
-      <c r="H60" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="I60" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J60" s="2">
-        <v>46336.25</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K60" s="2">
-        <v>46336.75</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L60" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3212,69 +3167,66 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="D61" t="s">
-        <v>160</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="F61" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G61" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="H61" t="s">
+        <v>31</v>
       </c>
       <c r="I61" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J61" s="2">
-        <v>46336.625</v>
+        <v>46337.625</v>
       </c>
       <c r="K61" s="2">
-        <v>46338.75</v>
+        <v>46338.041666666664</v>
       </c>
       <c r="L61" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>13</v>
+      </c>
+      <c r="C62" t="s">
+        <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F62" t="s">
-        <v>88</v>
-      </c>
-      <c r="G62" t="s">
-        <v>17</v>
-      </c>
-      <c r="H62" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="I62" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J62" s="2">
-        <v>46337.25</v>
+        <v>46337.913888888892</v>
       </c>
       <c r="K62" s="2">
-        <v>46337.75</v>
+        <v>46341.205555555556</v>
       </c>
       <c r="L62" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3282,348 +3234,345 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>46</v>
+        <v>154</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="F63" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="I63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J63" s="2">
-        <v>46337.333333333336</v>
+        <v>46337.913888888892</v>
       </c>
       <c r="K63" s="2">
-        <v>46337.833333333336</v>
+        <v>46341.205555555556</v>
       </c>
       <c r="L63" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B64" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="D64" t="s">
-        <v>164</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F64" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="I64" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J64" s="2">
-        <v>46337.333333333336</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K64" s="2">
-        <v>46339.333333333336</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L64" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B65" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C65" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="D65" t="s">
-        <v>114</v>
+        <v>157</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F65" t="s">
-        <v>54</v>
-      </c>
-      <c r="G65" t="s">
-        <v>55</v>
-      </c>
-      <c r="H65" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="I65" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="J65" s="2">
-        <v>46337.625</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K65" s="2">
-        <v>46338.041666666664</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L65" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="C66" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="D66" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="F66" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="I66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J66" s="2">
-        <v>46337.913888888892</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K66" s="2">
-        <v>46341.205555555556</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L66" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="C67" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="D67" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="F67" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="I67" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J67" s="2">
-        <v>46337.913888888892</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K67" s="2">
-        <v>46341.205555555556</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L67" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G68" t="s">
+        <v>31</v>
+      </c>
+      <c r="H68" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" t="s">
         <v>32</v>
       </c>
-      <c r="B68" t="s">
+      <c r="J68" s="2">
+        <v>46339.625</v>
+      </c>
+      <c r="K68" s="2">
+        <v>46340.041666666664</v>
+      </c>
+      <c r="L68" t="s">
         <v>33</v>
-      </c>
-      <c r="C68" t="s">
-        <v>69</v>
-      </c>
-      <c r="D68" t="s">
-        <v>168</v>
-      </c>
-      <c r="F68" t="s">
-        <v>72</v>
-      </c>
-      <c r="I68" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="2">
-        <v>46338.431250000001</v>
-      </c>
-      <c r="K68" s="2">
-        <v>46339.472916666666</v>
-      </c>
-      <c r="L68" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="C69" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D69" t="s">
-        <v>169</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="I69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J69" s="2">
-        <v>46338.709027777775</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K69" s="2">
-        <v>46339.584027777775</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L69" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C70" t="s">
-        <v>128</v>
+        <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>171</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="F70" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="I70" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J70" s="2">
-        <v>46339.291666666664</v>
+        <v>46340.416666666664</v>
       </c>
       <c r="K70" s="2">
-        <v>46340.666666666664</v>
+        <v>46340.75</v>
       </c>
       <c r="L70" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C71" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="D71" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F71" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="I71" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J71" s="2">
-        <v>46339.291666666664</v>
+        <v>46341.208333333336</v>
       </c>
       <c r="K71" s="2">
-        <v>46340.666666666664</v>
+        <v>46343.708333333336</v>
       </c>
       <c r="L71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B72" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C72" t="s">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="D72" t="s">
-        <v>53</v>
+        <v>165</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="F72" t="s">
-        <v>54</v>
-      </c>
-      <c r="G72" t="s">
-        <v>55</v>
-      </c>
-      <c r="H72" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="I72" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="J72" s="2">
-        <v>46339.625</v>
+        <v>46341.333333333336</v>
       </c>
       <c r="K72" s="2">
-        <v>46340.041666666664</v>
+        <v>46342.333333333336</v>
       </c>
       <c r="L72" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C73" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D73" t="s">
-        <v>173</v>
+        <v>167</v>
+      </c>
+      <c r="E73" s="1">
+        <v>57</v>
       </c>
       <c r="F73" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J73" s="2">
-        <v>46339.704861111109</v>
+        <v>46341.62777777778</v>
       </c>
       <c r="K73" s="2">
-        <v>46340.204861111109</v>
+        <v>46346.00277777778</v>
       </c>
       <c r="L73" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3634,25 +3583,34 @@
         <v>44</v>
       </c>
       <c r="C74" t="s">
+        <v>45</v>
+      </c>
+      <c r="D74" t="s">
+        <v>168</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F74" t="s">
+        <v>38</v>
+      </c>
+      <c r="G74" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" t="s">
+        <v>169</v>
+      </c>
+      <c r="I74" t="s">
         <v>48</v>
       </c>
-      <c r="D74" t="s">
+      <c r="J74" s="2">
+        <v>46342.25</v>
+      </c>
+      <c r="K74" s="2">
+        <v>46342.75</v>
+      </c>
+      <c r="L74" t="s">
         <v>49</v>
-      </c>
-      <c r="F74" t="s">
-        <v>47</v>
-      </c>
-      <c r="I74" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" s="2">
-        <v>46340.416666666664</v>
-      </c>
-      <c r="K74" s="2">
-        <v>46340.75</v>
-      </c>
-      <c r="L74" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3660,31 +3618,37 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C75" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="D75" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>89</v>
+      </c>
+      <c r="G75" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75" t="s">
+        <v>169</v>
       </c>
       <c r="I75" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J75" s="2">
-        <v>46341.208333333336</v>
+        <v>46342.25</v>
       </c>
       <c r="K75" s="2">
-        <v>46343.708333333336</v>
+        <v>46342.75</v>
       </c>
       <c r="L75" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3692,98 +3656,98 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C76" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D76" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F76" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="G76" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J76" s="2">
-        <v>46341.25</v>
+        <v>46342.25</v>
       </c>
       <c r="K76" s="2">
-        <v>46341.75</v>
+        <v>46342.75</v>
       </c>
       <c r="L76" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
-      </c>
-      <c r="C77" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="D77" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F77" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J77" s="2">
-        <v>46341.333333333336</v>
+        <v>46342.25</v>
       </c>
       <c r="K77" s="2">
-        <v>46342.333333333336</v>
+        <v>46344.25</v>
       </c>
       <c r="L77" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C78" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D78" t="s">
-        <v>180</v>
-      </c>
-      <c r="E78" s="1">
-        <v>57</v>
+        <v>172</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="F78" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="G78" t="s">
+        <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J78" s="2">
-        <v>46341.62777777778</v>
+        <v>46342.791666666664</v>
       </c>
       <c r="K78" s="2">
-        <v>46346.00277777778</v>
+        <v>46343.75</v>
       </c>
       <c r="L78" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3791,10 +3755,10 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C79" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D79" t="s">
         <v>176</v>
@@ -3803,22 +3767,19 @@
         <v>177</v>
       </c>
       <c r="F79" t="s">
-        <v>104</v>
-      </c>
-      <c r="G79" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="I79" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J79" s="2">
-        <v>46341.791666666664</v>
+        <v>46343.208333333336</v>
       </c>
       <c r="K79" s="2">
-        <v>46342.75</v>
+        <v>46345.125</v>
       </c>
       <c r="L79" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3826,37 +3787,34 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D80" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="F80" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="G80" t="s">
-        <v>17</v>
-      </c>
-      <c r="H80" t="s">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J80" s="2">
-        <v>46342.25</v>
+        <v>46343.25</v>
       </c>
       <c r="K80" s="2">
-        <v>46342.75</v>
+        <v>46343.75</v>
       </c>
       <c r="L80" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3864,37 +3822,37 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C81" t="s">
+        <v>45</v>
+      </c>
+      <c r="D81" t="s">
+        <v>180</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F81" t="s">
+        <v>38</v>
+      </c>
+      <c r="G81" t="s">
+        <v>18</v>
+      </c>
+      <c r="H81" t="s">
         <v>25</v>
       </c>
-      <c r="D81" t="s">
-        <v>183</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F81" t="s">
-        <v>104</v>
-      </c>
-      <c r="G81" t="s">
-        <v>17</v>
-      </c>
-      <c r="H81" t="s">
-        <v>182</v>
-      </c>
       <c r="I81" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J81" s="2">
-        <v>46342.25</v>
+        <v>46343.25</v>
       </c>
       <c r="K81" s="2">
-        <v>46342.75</v>
+        <v>46343.75</v>
       </c>
       <c r="L81" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3902,34 +3860,34 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D82" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F82" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G82" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J82" s="2">
-        <v>46342.25</v>
+        <v>46343.25</v>
       </c>
       <c r="K82" s="2">
-        <v>46342.75</v>
+        <v>46343.75</v>
       </c>
       <c r="L82" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3937,28 +3895,31 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>62</v>
+        <v>13</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F83" t="s">
-        <v>65</v>
+        <v>186</v>
       </c>
       <c r="I83" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J83" s="2">
-        <v>46342.25</v>
+        <v>46343.3125</v>
       </c>
       <c r="K83" s="2">
-        <v>46344.25</v>
+        <v>46346.604166666664</v>
       </c>
       <c r="L83" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3966,34 +3927,34 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C84" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D84" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F84" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G84" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J84" s="2">
-        <v>46342.791666666664</v>
+        <v>46343.791666666664</v>
       </c>
       <c r="K84" s="2">
-        <v>46343.75</v>
+        <v>46344.75</v>
       </c>
       <c r="L84" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4001,31 +3962,34 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C85" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D85" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="F85" t="s">
-        <v>140</v>
+        <v>89</v>
+      </c>
+      <c r="G85" t="s">
+        <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J85" s="2">
-        <v>46343.208333333336</v>
+        <v>46343.791666666664</v>
       </c>
       <c r="K85" s="2">
-        <v>46345.125</v>
+        <v>46344.75</v>
       </c>
       <c r="L85" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4036,69 +4000,54 @@
         <v>39</v>
       </c>
       <c r="C86" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D86" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F86" t="s">
         <v>42</v>
       </c>
-      <c r="G86" t="s">
-        <v>17</v>
-      </c>
-      <c r="H86" t="s">
-        <v>38</v>
-      </c>
       <c r="I86" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J86" s="2">
-        <v>46343.25</v>
+        <v>46344</v>
       </c>
       <c r="K86" s="2">
-        <v>46343.75</v>
+        <v>46346</v>
       </c>
       <c r="L86" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B87" t="s">
-        <v>77</v>
-      </c>
-      <c r="C87" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D87" t="s">
-        <v>193</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F87" t="s">
-        <v>42</v>
-      </c>
-      <c r="G87" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="I87" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J87" s="2">
-        <v>46343.25</v>
+        <v>46344.083333333336</v>
       </c>
       <c r="K87" s="2">
-        <v>46343.75</v>
+        <v>46345.208333333336</v>
       </c>
       <c r="L87" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4106,31 +4055,28 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="D88" t="s">
-        <v>195</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>196</v>
+        <v>112</v>
       </c>
       <c r="F88" t="s">
-        <v>197</v>
+        <v>24</v>
       </c>
       <c r="I88" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J88" s="2">
-        <v>46343.3125</v>
+        <v>46344.291666666664</v>
       </c>
       <c r="K88" s="2">
-        <v>46346.604166666664</v>
+        <v>46344.791666666664</v>
       </c>
       <c r="L88" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4138,34 +4084,34 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C89" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="D89" t="s">
-        <v>193</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="F89" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G89" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="H89" t="s">
+        <v>31</v>
       </c>
       <c r="I89" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J89" s="2">
-        <v>46343.791666666664</v>
+        <v>46344.625</v>
       </c>
       <c r="K89" s="2">
-        <v>46344.75</v>
+        <v>46345.041666666664</v>
       </c>
       <c r="L89" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4173,86 +4119,98 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C90" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="D90" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F90" t="s">
-        <v>65</v>
+        <v>38</v>
+      </c>
+      <c r="G90" t="s">
+        <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J90" s="2">
-        <v>46344</v>
+        <v>46345.25</v>
       </c>
       <c r="K90" s="2">
-        <v>46346</v>
+        <v>46345.75</v>
       </c>
       <c r="L90" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B91" t="s">
-        <v>33</v>
+        <v>66</v>
+      </c>
+      <c r="C91" t="s">
+        <v>67</v>
       </c>
       <c r="D91" t="s">
-        <v>200</v>
+        <v>192</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="F91" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="I91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J91" s="2">
-        <v>46344.083333333336</v>
+        <v>46345.291666666664</v>
       </c>
       <c r="K91" s="2">
-        <v>46345.208333333336</v>
+        <v>46346.166666666664</v>
       </c>
       <c r="L91" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B92" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C92" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="D92" t="s">
-        <v>127</v>
+        <v>194</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="F92" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I92" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J92" s="2">
-        <v>46344.291666666664</v>
+        <v>46346.23333333333</v>
       </c>
       <c r="K92" s="2">
-        <v>46344.791666666664</v>
+        <v>46347.275000000001</v>
       </c>
       <c r="L92" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4260,325 +4218,191 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C93" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="D93" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="F93" t="s">
-        <v>54</v>
-      </c>
-      <c r="G93" t="s">
-        <v>55</v>
-      </c>
-      <c r="H93" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="I93" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="J93" s="2">
-        <v>46344.625</v>
+        <v>46346.333333333336</v>
       </c>
       <c r="K93" s="2">
-        <v>46345.041666666664</v>
+        <v>46346.833333333336</v>
       </c>
       <c r="L93" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B94" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="D94" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F94" t="s">
-        <v>42</v>
-      </c>
-      <c r="G94" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="I94" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J94" s="2">
-        <v>46345.25</v>
+        <v>46346.395833333336</v>
       </c>
       <c r="K94" s="2">
-        <v>46345.75</v>
+        <v>46347.604166666664</v>
       </c>
       <c r="L94" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B95" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C95" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D95" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F95" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="I95" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J95" s="2">
-        <v>46345.291666666664</v>
+        <v>46346.395833333336</v>
       </c>
       <c r="K95" s="2">
-        <v>46346.166666666664</v>
+        <v>46347.604166666664</v>
       </c>
       <c r="L95" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B96" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C96" t="s">
-        <v>118</v>
+        <v>198</v>
       </c>
       <c r="D96" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F96" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="I96" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J96" s="2">
-        <v>46346.23333333333</v>
+        <v>46346.583333333336</v>
       </c>
       <c r="K96" s="2">
-        <v>46347.275000000001</v>
+        <v>46348.083333333336</v>
       </c>
       <c r="L96" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B97" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C97" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="D97" t="s">
-        <v>46</v>
+        <v>199</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="F97" t="s">
-        <v>47</v>
+        <v>186</v>
       </c>
       <c r="I97" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J97" s="2">
-        <v>46346.333333333336</v>
+        <v>46346.583333333336</v>
       </c>
       <c r="K97" s="2">
-        <v>46346.833333333336</v>
+        <v>46348.083333333336</v>
       </c>
       <c r="L97" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" t="s">
+        <v>28</v>
+      </c>
+      <c r="D98" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98" t="s">
+        <v>30</v>
+      </c>
+      <c r="G98" t="s">
+        <v>31</v>
+      </c>
+      <c r="H98" t="s">
+        <v>31</v>
+      </c>
+      <c r="I98" t="s">
         <v>32</v>
       </c>
-      <c r="B98" t="s">
+      <c r="J98" s="2">
+        <v>46346.625</v>
+      </c>
+      <c r="K98" s="2">
+        <v>46347.041666666664</v>
+      </c>
+      <c r="L98" t="s">
         <v>33</v>
-      </c>
-      <c r="C98" t="s">
-        <v>108</v>
-      </c>
-      <c r="D98" t="s">
-        <v>207</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F98" t="s">
-        <v>140</v>
-      </c>
-      <c r="I98" t="s">
-        <v>18</v>
-      </c>
-      <c r="J98" s="2">
-        <v>46346.395833333336</v>
-      </c>
-      <c r="K98" s="2">
-        <v>46347.604166666664</v>
-      </c>
-      <c r="L98" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12">
-      <c r="A99" t="s">
-        <v>32</v>
-      </c>
-      <c r="B99" t="s">
-        <v>33</v>
-      </c>
-      <c r="C99" t="s">
-        <v>108</v>
-      </c>
-      <c r="D99" t="s">
-        <v>207</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F99" t="s">
-        <v>140</v>
-      </c>
-      <c r="I99" t="s">
-        <v>18</v>
-      </c>
-      <c r="J99" s="2">
-        <v>46346.395833333336</v>
-      </c>
-      <c r="K99" s="2">
-        <v>46347.604166666664</v>
-      </c>
-      <c r="L99" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12">
-      <c r="A100" t="s">
-        <v>32</v>
-      </c>
-      <c r="B100" t="s">
-        <v>33</v>
-      </c>
-      <c r="C100" t="s">
-        <v>34</v>
-      </c>
-      <c r="D100" t="s">
-        <v>209</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F100" t="s">
-        <v>197</v>
-      </c>
-      <c r="I100" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="2">
-        <v>46346.583333333336</v>
-      </c>
-      <c r="K100" s="2">
-        <v>46348.083333333336</v>
-      </c>
-      <c r="L100" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12">
-      <c r="A101" t="s">
-        <v>32</v>
-      </c>
-      <c r="B101" t="s">
-        <v>33</v>
-      </c>
-      <c r="C101" t="s">
-        <v>34</v>
-      </c>
-      <c r="D101" t="s">
-        <v>209</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F101" t="s">
-        <v>197</v>
-      </c>
-      <c r="I101" t="s">
-        <v>18</v>
-      </c>
-      <c r="J101" s="2">
-        <v>46346.583333333336</v>
-      </c>
-      <c r="K101" s="2">
-        <v>46348.083333333336</v>
-      </c>
-      <c r="L101" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12">
-      <c r="A102" t="s">
-        <v>12</v>
-      </c>
-      <c r="B102" t="s">
-        <v>51</v>
-      </c>
-      <c r="C102" t="s">
-        <v>52</v>
-      </c>
-      <c r="D102" t="s">
-        <v>53</v>
-      </c>
-      <c r="F102" t="s">
-        <v>54</v>
-      </c>
-      <c r="G102" t="s">
-        <v>55</v>
-      </c>
-      <c r="H102" t="s">
-        <v>55</v>
-      </c>
-      <c r="I102" t="s">
-        <v>56</v>
-      </c>
-      <c r="J102" s="2">
-        <v>46346.625</v>
-      </c>
-      <c r="K102" s="2">
-        <v>46347.041666666664</v>
-      </c>
-      <c r="L102" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4590,6 +4414,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4598,7 +4430,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4736,32 +4568,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
--- a/data/vessels/2026-10-30.xlsx
+++ b/data/vessels/2026-10-30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="470379" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF28954D-A0AA-434A-87CC-755FA5FB5F65}"/>
+  <xr:revisionPtr revIDLastSave="470689" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF21762E-4AF4-40AB-86E2-210627A9B490}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="201">
   <si>
     <t>Harbor</t>
   </si>
@@ -119,289 +119,289 @@
     <t>SSA Marine</t>
   </si>
   <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639W</t>
+  </si>
+  <si>
+    <t>ONE</t>
+  </si>
+  <si>
     <t>In transit</t>
   </si>
   <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>EVER MODE</t>
+  </si>
+  <si>
+    <t>010W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>Ad Hoc</t>
+  </si>
+  <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>EB Service 2</t>
+  </si>
+  <si>
+    <t>NADI CHIEF</t>
+  </si>
+  <si>
+    <t>015E/016W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CYPRESS</t>
+  </si>
+  <si>
+    <t>CPN06/CPN07</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>SWIFT ACE</t>
+  </si>
+  <si>
+    <t>152A</t>
+  </si>
+  <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>ONE SYNERGY</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC643R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>SM TIANJIN</t>
+  </si>
+  <si>
+    <t>2606E/2606W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>EUROPEAN HIGHWAY</t>
+  </si>
+  <si>
+    <t>285A</t>
+  </si>
+  <si>
+    <t>TPN</t>
+  </si>
+  <si>
+    <t>EVER SMILE</t>
+  </si>
+  <si>
+    <t>136W</t>
+  </si>
+  <si>
+    <t>Everport Terminal Services</t>
+  </si>
+  <si>
+    <t>MSC IVANA</t>
+  </si>
+  <si>
+    <t>UK642R</t>
+  </si>
+  <si>
+    <t>HYUNDAI FORWARD</t>
+  </si>
+  <si>
+    <t>PN32640E</t>
+  </si>
+  <si>
+    <t>HMM</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>MORNING LUCY</t>
+  </si>
+  <si>
+    <t>A6179</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>ONE MAJESTY</t>
+  </si>
+  <si>
+    <t>PN12641W</t>
+  </si>
+  <si>
     <t>TOTE</t>
   </si>
   <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>COSCO SANTOS</t>
+  </si>
+  <si>
+    <t>102N/102E</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>MSC FLORA</t>
+  </si>
+  <si>
+    <t>MC644R</t>
+  </si>
+  <si>
+    <t>KW665</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD COLUMBIA</t>
+  </si>
+  <si>
+    <t>156E/157W</t>
+  </si>
+  <si>
+    <t>GLOVIS TRUST</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
+    <t>MSC SABRINA</t>
+  </si>
+  <si>
+    <t>MC645R</t>
+  </si>
+  <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
+    <t>156E</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL SEATTLE</t>
+  </si>
+  <si>
+    <t>046E/046W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>EVER MOST</t>
+  </si>
+  <si>
+    <t>011W</t>
+  </si>
+  <si>
     <t>Tote - AK2</t>
   </si>
   <si>
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>Waiting 2.9 days</t>
-  </si>
-  <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639W</t>
-  </si>
-  <si>
-    <t>ONE</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>EVER MODE</t>
-  </si>
-  <si>
-    <t>010W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>Ad Hoc</t>
-  </si>
-  <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>Not available</t>
-  </si>
-  <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>T18</t>
-  </si>
-  <si>
-    <t>EB Service 2</t>
-  </si>
-  <si>
-    <t>NADI CHIEF</t>
-  </si>
-  <si>
-    <t>015E/016W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CYPRESS</t>
-  </si>
-  <si>
-    <t>CPN06/CPN07</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>SWIFT ACE</t>
-  </si>
-  <si>
-    <t>152A</t>
-  </si>
-  <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>ONE SYNERGY</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC643R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>SM TIANJIN</t>
-  </si>
-  <si>
-    <t>2606E/2606W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>EUROPEAN HIGHWAY</t>
-  </si>
-  <si>
-    <t>285A</t>
-  </si>
-  <si>
-    <t>TPN</t>
-  </si>
-  <si>
-    <t>EVER SMILE</t>
-  </si>
-  <si>
-    <t>136W</t>
-  </si>
-  <si>
-    <t>Everport Terminal Services</t>
-  </si>
-  <si>
-    <t>MSC IVANA</t>
-  </si>
-  <si>
-    <t>UK642R</t>
-  </si>
-  <si>
-    <t>HYUNDAI FORWARD</t>
-  </si>
-  <si>
-    <t>PN32640E</t>
-  </si>
-  <si>
-    <t>HMM</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>MORNING LUCY</t>
-  </si>
-  <si>
-    <t>A6179</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>ONE MAJESTY</t>
-  </si>
-  <si>
-    <t>PN12641W</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>COSCO SANTOS</t>
-  </si>
-  <si>
-    <t>102N/102E</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>MSC FLORA</t>
-  </si>
-  <si>
-    <t>MC644R</t>
-  </si>
-  <si>
-    <t>KW665</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD COLUMBIA</t>
-  </si>
-  <si>
-    <t>156E/157W</t>
-  </si>
-  <si>
-    <t>GLOVIS TRUST</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>MSC SABRINA</t>
-  </si>
-  <si>
-    <t>MC645R</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>156E</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL SEATTLE</t>
-  </si>
-  <si>
-    <t>046E/046W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>EVER MOST</t>
-  </si>
-  <si>
-    <t>011W</t>
+    <t>Waiting 3 days</t>
   </si>
   <si>
     <t>TONGALA</t>
@@ -545,6 +545,12 @@
     <t>CMA CGM ARKANSAS</t>
   </si>
   <si>
+    <t>GLORIOUS ACE</t>
+  </si>
+  <si>
+    <t>113A</t>
+  </si>
+  <si>
     <t>WISDOM ACE</t>
   </si>
   <si>
@@ -557,12 +563,6 @@
     <t>ED617</t>
   </si>
   <si>
-    <t>GLORIOUS ACE</t>
-  </si>
-  <si>
-    <t>113A</t>
-  </si>
-  <si>
     <t>EVER MAGUS</t>
   </si>
   <si>
@@ -575,22 +575,22 @@
     <t>PN32642W</t>
   </si>
   <si>
+    <t>TOURMALINE ACE</t>
+  </si>
+  <si>
+    <t>013A</t>
+  </si>
+  <si>
+    <t>EUPHONY ACE</t>
+  </si>
+  <si>
+    <t>166A</t>
+  </si>
+  <si>
     <t>OTELLO</t>
   </si>
   <si>
     <t>A6193</t>
-  </si>
-  <si>
-    <t>EUPHONY ACE</t>
-  </si>
-  <si>
-    <t>166A</t>
-  </si>
-  <si>
-    <t>TOURMALINE ACE</t>
-  </si>
-  <si>
-    <t>013A</t>
   </si>
   <si>
     <t>MAERSK SARNIA</t>
@@ -714,10 +714,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L98" totalsRowShown="0">
-  <autoFilter ref="A1:L98" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L98">
-    <sortCondition ref="J2:J98"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L97" totalsRowShown="0">
+  <autoFilter ref="A1:L97" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L97">
+    <sortCondition ref="J2:J97"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1054,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1208,7 +1208,7 @@
         <v>46326.125</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1216,37 +1216,34 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E5" s="1">
-        <v>26172</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2">
         <v>46325.625</v>
       </c>
       <c r="K5" s="2">
-        <v>46326.041666666664</v>
+        <v>46327.75</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1254,19 +1251,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
         <v>18</v>
@@ -1280,37 +1277,40 @@
       <c r="K6" s="2">
         <v>46327.75</v>
       </c>
+      <c r="L6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
         <v>35</v>
       </c>
-      <c r="D7" t="s">
+      <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
       <c r="I7" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="2">
-        <v>46325.625</v>
+        <v>46325.666666666664</v>
       </c>
       <c r="K7" s="2">
-        <v>46327.75</v>
+        <v>46327.25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1318,19 +1318,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
@@ -1342,7 +1342,7 @@
         <v>46327.25</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1350,36 +1350,39 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
         <v>41</v>
       </c>
-      <c r="F9" t="s">
+      <c r="J9" s="2">
+        <v>46325.916666666664</v>
+      </c>
+      <c r="K9" s="2">
+        <v>46326.708333333336</v>
+      </c>
+      <c r="L9" t="s">
         <v>42</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="2">
-        <v>46325.666666666664</v>
-      </c>
-      <c r="K9" s="2">
-        <v>46327.25</v>
-      </c>
-      <c r="L9" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
         <v>44</v>
@@ -1394,92 +1397,92 @@
         <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J10" s="2">
         <v>46325.916666666664</v>
       </c>
       <c r="K10" s="2">
-        <v>46326.708333333336</v>
+        <v>46327.083333333336</v>
       </c>
       <c r="L10" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
         <v>50</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="2">
-        <v>46325.916666666664</v>
+        <v>46326.208333333336</v>
       </c>
       <c r="K11" s="2">
-        <v>46327.083333333336</v>
+        <v>46328.75</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
         <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J12" s="2">
-        <v>46326.208333333336</v>
+        <v>46327.208333333336</v>
       </c>
       <c r="K12" s="2">
-        <v>46328.75</v>
+        <v>46327.791666666664</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1487,34 +1490,34 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J13" s="2">
-        <v>46327.208333333336</v>
+        <v>46327.625</v>
       </c>
       <c r="K13" s="2">
-        <v>46327.791666666664</v>
+        <v>46334.333333333336</v>
       </c>
       <c r="L13" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1525,16 +1528,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
         <v>18</v>
@@ -1549,27 +1552,27 @@
         <v>46334.333333333336</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" s="1">
-        <v>2</v>
+        <v>61</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
@@ -1578,118 +1581,118 @@
         <v>19</v>
       </c>
       <c r="J15" s="2">
-        <v>46327.625</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K15" s="2">
-        <v>46334.333333333336</v>
+        <v>46328.75</v>
       </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J16" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.833333333336</v>
       </c>
       <c r="K16" s="2">
         <v>46328.75</v>
       </c>
       <c r="L16" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
         <v>44</v>
       </c>
-      <c r="C17" t="s">
-        <v>45</v>
-      </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G17" t="s">
         <v>18</v>
       </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J17" s="2">
-        <v>46327.833333333336</v>
+        <v>46328.208333333336</v>
       </c>
       <c r="K17" s="2">
         <v>46328.75</v>
       </c>
       <c r="L17" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="G18" t="s">
         <v>18</v>
       </c>
-      <c r="H18" t="s">
-        <v>25</v>
-      </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J18" s="2">
-        <v>46328.208333333336</v>
+        <v>46328.25</v>
       </c>
       <c r="K18" s="2">
-        <v>46328.75</v>
+        <v>46328.708333333336</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1697,110 +1700,110 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="H19" t="s">
+        <v>72</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J19" s="2">
-        <v>46328.25</v>
+        <v>46329.208333333336</v>
       </c>
       <c r="K19" s="2">
-        <v>46328.708333333336</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="2">
+        <v>46329.291666666664</v>
+      </c>
+      <c r="K20" s="2">
+        <v>46331.166666666664</v>
+      </c>
+      <c r="L20" t="s">
         <v>42</v>
-      </c>
-      <c r="G20" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" t="s">
-        <v>79</v>
-      </c>
-      <c r="I20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" s="2">
-        <v>46329.208333333336</v>
-      </c>
-      <c r="K20" s="2">
-        <v>46331.791666666664</v>
-      </c>
-      <c r="L20" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s">
         <v>18</v>
       </c>
-      <c r="H21" t="s">
-        <v>25</v>
-      </c>
       <c r="I21" t="s">
         <v>19</v>
       </c>
       <c r="J21" s="2">
-        <v>46329.291666666664</v>
+        <v>46329.625</v>
       </c>
       <c r="K21" s="2">
-        <v>46331.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L21" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1808,34 +1811,34 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>24</v>
+      </c>
+      <c r="H22" t="s">
+        <v>25</v>
       </c>
       <c r="I22" t="s">
         <v>19</v>
       </c>
       <c r="J22" s="2">
-        <v>46329.625</v>
+        <v>46330.104166666664</v>
       </c>
       <c r="K22" s="2">
-        <v>46331.75</v>
+        <v>46330.916666666664</v>
       </c>
       <c r="L22" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1843,34 +1846,34 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J23" s="2">
-        <v>46330.104166666664</v>
+        <v>46330.25</v>
       </c>
       <c r="K23" s="2">
-        <v>46330.916666666664</v>
+        <v>46330.75</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1878,34 +1881,34 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="G24" t="s">
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J24" s="2">
         <v>46330.25</v>
       </c>
       <c r="K24" s="2">
-        <v>46330.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L24" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1913,57 +1916,57 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" t="s">
         <v>90</v>
       </c>
-      <c r="D25" t="s">
+      <c r="H25" t="s">
+        <v>90</v>
+      </c>
+      <c r="I25" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" t="s">
-        <v>19</v>
-      </c>
       <c r="J25" s="2">
-        <v>46330.25</v>
+        <v>46330.625</v>
       </c>
       <c r="K25" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.041666666664</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" t="s">
         <v>93</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" t="s">
         <v>95</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>96</v>
-      </c>
-      <c r="G26" t="s">
-        <v>97</v>
       </c>
       <c r="I26" t="s">
         <v>19</v>
@@ -1975,287 +1978,287 @@
         <v>46331.75</v>
       </c>
       <c r="L26" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D27" t="s">
-        <v>99</v>
-      </c>
       <c r="F27" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="G27" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J27" s="2">
-        <v>46330.625</v>
+        <v>46330.708333333336</v>
       </c>
       <c r="K27" s="2">
-        <v>46331.041666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F28" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J28" s="2">
-        <v>46330.708333333336</v>
+        <v>46330.791666666664</v>
       </c>
       <c r="K28" s="2">
         <v>46331.75</v>
       </c>
       <c r="L28" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
         <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F29" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="G29" t="s">
-        <v>18</v>
+        <v>49</v>
+      </c>
+      <c r="H29" t="s">
+        <v>25</v>
       </c>
       <c r="I29" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J29" s="2">
-        <v>46330.791666666664</v>
+        <v>46331.25</v>
       </c>
       <c r="K29" s="2">
-        <v>46331.75</v>
+        <v>46332.708333333336</v>
       </c>
       <c r="L29" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s">
         <v>103</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" s="1">
+        <v>11</v>
+      </c>
+      <c r="F30" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
       <c r="G30" t="s">
-        <v>56</v>
-      </c>
-      <c r="H30" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J30" s="2">
-        <v>46331.25</v>
+        <v>46331.270833333336</v>
       </c>
       <c r="K30" s="2">
-        <v>46332.708333333336</v>
+        <v>46331.729166666664</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D31" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="1">
-        <v>11</v>
-      </c>
       <c r="F31" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="G31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J31" s="2">
-        <v>46331.270833333336</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K31" s="2">
-        <v>46331.729166666664</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
+      </c>
+      <c r="E32" s="1">
+        <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="G32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J32" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.833333333336</v>
       </c>
       <c r="K32" s="2">
         <v>46332.166666666664</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
-      </c>
-      <c r="E33" s="1">
-        <v>10</v>
+        <v>101</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="F33" t="s">
-        <v>107</v>
-      </c>
-      <c r="G33" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I33" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J33" s="2">
-        <v>46331.833333333336</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K33" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L33" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F34" t="s">
-        <v>55</v>
+        <v>24</v>
+      </c>
+      <c r="G34" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" t="s">
+        <v>25</v>
       </c>
       <c r="I34" t="s">
         <v>19</v>
       </c>
       <c r="J34" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.104166666664</v>
       </c>
       <c r="K34" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.916666666664</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2263,104 +2266,104 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
-        <v>112</v>
+        <v>107</v>
+      </c>
+      <c r="E35" s="1">
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="G35" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J35" s="2">
-        <v>46332.104166666664</v>
+        <v>46332.208333333336</v>
       </c>
       <c r="K35" s="2">
-        <v>46332.916666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L35" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
         <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
-      </c>
-      <c r="E36" s="1">
-        <v>10</v>
+        <v>111</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="F36" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G36" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="I36" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J36" s="2">
-        <v>46332.208333333336</v>
+        <v>46332.25</v>
       </c>
       <c r="K36" s="2">
-        <v>46332.75</v>
+        <v>46333.166666666664</v>
       </c>
       <c r="L36" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" s="1" t="s">
         <v>115</v>
       </c>
       <c r="F37" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="G37" t="s">
-        <v>117</v>
+        <v>24</v>
+      </c>
+      <c r="H37" t="s">
+        <v>25</v>
       </c>
       <c r="I37" t="s">
         <v>19</v>
       </c>
       <c r="J37" s="2">
-        <v>46332.25</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K37" s="2">
-        <v>46333.166666666664</v>
+        <v>46333.125</v>
       </c>
       <c r="L37" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2368,34 +2371,31 @@
         <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C38" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>118</v>
+        <v>116</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="F38" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G38" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="I38" t="s">
         <v>19</v>
       </c>
       <c r="J38" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.5</v>
       </c>
       <c r="K38" s="2">
-        <v>46333.125</v>
+        <v>46334.208333333336</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2403,19 +2403,19 @@
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F39" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G39" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I39" t="s">
         <v>19</v>
@@ -2427,7 +2427,7 @@
         <v>46334.208333333336</v>
       </c>
       <c r="L39" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2435,31 +2435,34 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>86</v>
+      </c>
+      <c r="C40" t="s">
+        <v>118</v>
       </c>
       <c r="D40" t="s">
         <v>119</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" t="s">
+        <v>89</v>
+      </c>
+      <c r="G40" t="s">
+        <v>90</v>
+      </c>
+      <c r="H40" t="s">
+        <v>90</v>
+      </c>
+      <c r="I40" t="s">
+        <v>91</v>
+      </c>
+      <c r="J40" s="2">
+        <v>46332.625</v>
+      </c>
+      <c r="K40" s="2">
+        <v>46333.041666666664</v>
+      </c>
+      <c r="L40" t="s">
         <v>120</v>
-      </c>
-      <c r="F40" t="s">
-        <v>42</v>
-      </c>
-      <c r="G40" t="s">
-        <v>43</v>
-      </c>
-      <c r="I40" t="s">
-        <v>19</v>
-      </c>
-      <c r="J40" s="2">
-        <v>46332.5</v>
-      </c>
-      <c r="K40" s="2">
-        <v>46334.208333333336</v>
-      </c>
-      <c r="L40" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2467,34 +2470,37 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>121</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H41" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="I41" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J41" s="2">
-        <v>46332.625</v>
+        <v>46333.25</v>
       </c>
       <c r="K41" s="2">
-        <v>46333.041666666664</v>
+        <v>46333.75</v>
       </c>
       <c r="L41" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2502,37 +2508,31 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="D42" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F42" t="s">
-        <v>89</v>
-      </c>
-      <c r="G42" t="s">
-        <v>18</v>
-      </c>
-      <c r="H42" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I42" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J42" s="2">
-        <v>46333.25</v>
+        <v>46333.625</v>
       </c>
       <c r="K42" s="2">
-        <v>46333.75</v>
+        <v>46336.166666666664</v>
       </c>
       <c r="L42" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2540,31 +2540,37 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="D43" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F43" t="s">
-        <v>126</v>
+        <v>82</v>
+      </c>
+      <c r="G43" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" t="s">
+        <v>123</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J43" s="2">
-        <v>46333.625</v>
+        <v>46333.791666666664</v>
       </c>
       <c r="K43" s="2">
-        <v>46336.166666666664</v>
+        <v>46334.75</v>
       </c>
       <c r="L43" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2572,37 +2578,34 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D44" t="s">
-        <v>121</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="E44" s="1">
+        <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="G44" t="s">
         <v>18</v>
       </c>
-      <c r="H44" t="s">
-        <v>123</v>
-      </c>
       <c r="I44" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J44" s="2">
-        <v>46333.791666666664</v>
+        <v>46334.625</v>
       </c>
       <c r="K44" s="2">
-        <v>46334.75</v>
+        <v>46339.75</v>
       </c>
       <c r="L44" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2613,16 +2616,16 @@
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" s="1">
-        <v>11</v>
+        <v>129</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="F45" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G45" t="s">
         <v>18</v>
@@ -2634,77 +2637,77 @@
         <v>46334.625</v>
       </c>
       <c r="K45" s="2">
-        <v>46339.75</v>
+        <v>46337.75</v>
       </c>
       <c r="L45" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F46" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
       </c>
       <c r="J46" s="2">
-        <v>46334.625</v>
+        <v>46334.75</v>
       </c>
       <c r="K46" s="2">
         <v>46337.75</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C47" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F47" t="s">
-        <v>60</v>
+        <v>30</v>
+      </c>
+      <c r="G47" t="s">
+        <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J47" s="2">
-        <v>46334.75</v>
+        <v>46335.25</v>
       </c>
       <c r="K47" s="2">
-        <v>46337.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L47" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2712,25 +2715,25 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D48" t="s">
-        <v>133</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="G48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J48" s="2">
         <v>46335.25</v>
@@ -2739,62 +2742,62 @@
         <v>46335.75</v>
       </c>
       <c r="L48" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="D49" t="s">
-        <v>135</v>
-      </c>
-      <c r="E49" s="1">
-        <v>1</v>
+        <v>137</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="F49" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="G49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J49" s="2">
-        <v>46335.25</v>
+        <v>46335.291666666664</v>
       </c>
       <c r="K49" s="2">
-        <v>46335.75</v>
+        <v>46337.166666666664</v>
       </c>
       <c r="L49" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
         <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F50" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G50" t="s">
         <v>18</v>
@@ -2803,48 +2806,48 @@
         <v>19</v>
       </c>
       <c r="J50" s="2">
-        <v>46335.291666666664</v>
+        <v>46335.708333333336</v>
       </c>
       <c r="K50" s="2">
-        <v>46337.166666666664</v>
+        <v>46337.75</v>
       </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="D51" t="s">
-        <v>139</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="G51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J51" s="2">
-        <v>46335.708333333336</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K51" s="2">
-        <v>46337.75</v>
+        <v>46336.75</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2852,34 +2855,37 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C52" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
-      </c>
-      <c r="E52" s="1">
-        <v>1</v>
+        <v>141</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="F52" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="G52" t="s">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="H52" t="s">
+        <v>72</v>
       </c>
       <c r="I52" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J52" s="2">
-        <v>46335.791666666664</v>
+        <v>46336.208333333336</v>
       </c>
       <c r="K52" s="2">
-        <v>46336.75</v>
+        <v>46340.708333333336</v>
       </c>
       <c r="L52" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2887,10 +2893,10 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
         <v>141</v>
@@ -2899,13 +2905,13 @@
         <v>142</v>
       </c>
       <c r="F53" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G53" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H53" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="I53" t="s">
         <v>19</v>
@@ -2917,7 +2923,7 @@
         <v>46340.708333333336</v>
       </c>
       <c r="L53" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2925,37 +2931,34 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="D54" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F54" t="s">
+        <v>145</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" t="s">
+        <v>41</v>
+      </c>
+      <c r="J54" s="2">
+        <v>46336.25</v>
+      </c>
+      <c r="K54" s="2">
+        <v>46336.75</v>
+      </c>
+      <c r="L54" t="s">
         <v>42</v>
-      </c>
-      <c r="G54" t="s">
-        <v>43</v>
-      </c>
-      <c r="H54" t="s">
-        <v>79</v>
-      </c>
-      <c r="I54" t="s">
-        <v>19</v>
-      </c>
-      <c r="J54" s="2">
-        <v>46336.208333333336</v>
-      </c>
-      <c r="K54" s="2">
-        <v>46340.708333333336</v>
-      </c>
-      <c r="L54" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -2963,25 +2966,28 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>143</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
+      </c>
+      <c r="E55" s="1">
+        <v>13</v>
       </c>
       <c r="F55" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="G55" t="s">
-        <v>18</v>
+        <v>114</v>
+      </c>
+      <c r="H55" t="s">
+        <v>123</v>
       </c>
       <c r="I55" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J55" s="2">
         <v>46336.25</v>
@@ -2990,7 +2996,7 @@
         <v>46336.75</v>
       </c>
       <c r="L55" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -2998,124 +3004,118 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
-      </c>
-      <c r="E56" s="1">
-        <v>13</v>
+        <v>147</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="F56" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G56" t="s">
-        <v>117</v>
-      </c>
-      <c r="H56" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J56" s="2">
-        <v>46336.25</v>
+        <v>46336.625</v>
       </c>
       <c r="K56" s="2">
-        <v>46336.75</v>
+        <v>46338.75</v>
       </c>
       <c r="L56" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
-      </c>
-      <c r="C57" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F57" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G57" t="s">
         <v>18</v>
       </c>
+      <c r="H57" t="s">
+        <v>25</v>
+      </c>
       <c r="I57" t="s">
         <v>19</v>
       </c>
       <c r="J57" s="2">
-        <v>46336.625</v>
+        <v>46337.25</v>
       </c>
       <c r="K57" s="2">
-        <v>46338.75</v>
+        <v>46337.75</v>
       </c>
       <c r="L57" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>51</v>
+        <v>21</v>
+      </c>
+      <c r="C58" t="s">
+        <v>78</v>
       </c>
       <c r="D58" t="s">
-        <v>149</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F58" t="s">
-        <v>73</v>
-      </c>
-      <c r="G58" t="s">
-        <v>18</v>
-      </c>
-      <c r="H58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I58" t="s">
         <v>19</v>
       </c>
       <c r="J58" s="2">
-        <v>46337.25</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K58" s="2">
-        <v>46337.75</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L58" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="C59" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="D59" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="F59" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
@@ -3124,42 +3124,45 @@
         <v>46337.333333333336</v>
       </c>
       <c r="K59" s="2">
-        <v>46337.833333333336</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L59" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s">
-        <v>152</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>153</v>
+        <v>88</v>
       </c>
       <c r="F60" t="s">
-        <v>70</v>
+        <v>89</v>
+      </c>
+      <c r="G60" t="s">
+        <v>90</v>
+      </c>
+      <c r="H60" t="s">
+        <v>90</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="J60" s="2">
-        <v>46337.333333333336</v>
+        <v>46337.625</v>
       </c>
       <c r="K60" s="2">
-        <v>46339.333333333336</v>
+        <v>46338.041666666664</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3167,34 +3170,31 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>99</v>
+        <v>154</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="F61" t="s">
-        <v>30</v>
-      </c>
-      <c r="G61" t="s">
-        <v>31</v>
-      </c>
-      <c r="H61" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="I61" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J61" s="2">
-        <v>46337.625</v>
+        <v>46337.913888888892</v>
       </c>
       <c r="K61" s="2">
-        <v>46338.041666666664</v>
+        <v>46341.205555555556</v>
       </c>
       <c r="L61" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3226,111 +3226,111 @@
         <v>46341.205555555556</v>
       </c>
       <c r="L62" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D63" t="s">
-        <v>154</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F63" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="I63" t="s">
         <v>19</v>
       </c>
       <c r="J63" s="2">
-        <v>46337.913888888892</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K63" s="2">
-        <v>46341.205555555556</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B64" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D64" t="s">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F64" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I64" t="s">
         <v>19</v>
       </c>
       <c r="J64" s="2">
-        <v>46338.431250000001</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K64" s="2">
-        <v>46339.472916666666</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B65" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="C65" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="D65" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="I65" t="s">
         <v>19</v>
       </c>
       <c r="J65" s="2">
-        <v>46338.709027777775</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K65" s="2">
-        <v>46339.584027777775</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L65" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C66" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D66" t="s">
         <v>159</v>
@@ -3339,7 +3339,7 @@
         <v>160</v>
       </c>
       <c r="F66" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I66" t="s">
         <v>19</v>
@@ -3351,39 +3351,42 @@
         <v>46340.666666666664</v>
       </c>
       <c r="L66" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>159</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="F67" t="s">
-        <v>116</v>
+        <v>89</v>
+      </c>
+      <c r="G67" t="s">
+        <v>90</v>
+      </c>
+      <c r="H67" t="s">
+        <v>90</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="J67" s="2">
-        <v>46339.291666666664</v>
+        <v>46339.625</v>
       </c>
       <c r="K67" s="2">
-        <v>46340.666666666664</v>
+        <v>46340.041666666664</v>
       </c>
       <c r="L67" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3391,34 +3394,28 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>30</v>
-      </c>
-      <c r="G68" t="s">
-        <v>31</v>
-      </c>
-      <c r="H68" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I68" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J68" s="2">
-        <v>46339.625</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K68" s="2">
-        <v>46340.041666666664</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L68" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3429,10 +3426,10 @@
         <v>21</v>
       </c>
       <c r="C69" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="D69" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="F69" t="s">
         <v>24</v>
@@ -3441,13 +3438,13 @@
         <v>19</v>
       </c>
       <c r="J69" s="2">
-        <v>46339.704861111109</v>
+        <v>46340.416666666664</v>
       </c>
       <c r="K69" s="2">
-        <v>46340.204861111109</v>
+        <v>46340.75</v>
       </c>
       <c r="L69" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3455,124 +3452,130 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>162</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="F70" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="I70" t="s">
         <v>19</v>
       </c>
       <c r="J70" s="2">
-        <v>46340.416666666664</v>
+        <v>46341.208333333336</v>
       </c>
       <c r="K70" s="2">
-        <v>46340.75</v>
+        <v>46343.708333333336</v>
       </c>
       <c r="L70" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C71" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="D71" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F71" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="I71" t="s">
         <v>19</v>
       </c>
       <c r="J71" s="2">
-        <v>46341.208333333336</v>
+        <v>46341.333333333336</v>
       </c>
       <c r="K71" s="2">
-        <v>46343.708333333336</v>
+        <v>46342.333333333336</v>
       </c>
       <c r="L71" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
+        <v>43</v>
+      </c>
+      <c r="B72" t="s">
+        <v>44</v>
+      </c>
+      <c r="C72" t="s">
         <v>50</v>
       </c>
-      <c r="B72" t="s">
-        <v>66</v>
-      </c>
-      <c r="C72" t="s">
-        <v>136</v>
-      </c>
       <c r="D72" t="s">
-        <v>165</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
+      </c>
+      <c r="E72" s="1">
+        <v>57</v>
       </c>
       <c r="F72" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="I72" t="s">
         <v>19</v>
       </c>
       <c r="J72" s="2">
-        <v>46341.333333333336</v>
+        <v>46341.62777777778</v>
       </c>
       <c r="K72" s="2">
-        <v>46342.333333333336</v>
+        <v>46346.00277777778</v>
       </c>
       <c r="L72" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C73" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D73" t="s">
-        <v>167</v>
-      </c>
-      <c r="E73" s="1">
-        <v>57</v>
+        <v>168</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="F73" t="s">
-        <v>60</v>
+        <v>30</v>
+      </c>
+      <c r="G73" t="s">
+        <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J73" s="2">
-        <v>46341.62777777778</v>
+        <v>46342.25</v>
       </c>
       <c r="K73" s="2">
-        <v>46346.00277777778</v>
+        <v>46342.75</v>
       </c>
       <c r="L73" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3580,28 +3583,28 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C74" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D74" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>134</v>
       </c>
       <c r="F74" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G74" t="s">
         <v>18</v>
       </c>
       <c r="H74" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I74" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J74" s="2">
         <v>46342.25</v>
@@ -3610,7 +3613,7 @@
         <v>46342.75</v>
       </c>
       <c r="L74" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3618,28 +3621,28 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C75" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D75" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F75" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G75" t="s">
         <v>18</v>
       </c>
       <c r="H75" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I75" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J75" s="2">
         <v>46342.25</v>
@@ -3648,7 +3651,7 @@
         <v>46342.75</v>
       </c>
       <c r="L75" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3656,34 +3659,28 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>61</v>
-      </c>
-      <c r="C76" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D76" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
-        <v>38</v>
-      </c>
-      <c r="G76" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I76" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J76" s="2">
         <v>46342.25</v>
       </c>
       <c r="K76" s="2">
-        <v>46342.75</v>
+        <v>46344.25</v>
       </c>
       <c r="L76" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3691,28 +3688,34 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="C77" t="s">
+        <v>38</v>
       </c>
       <c r="D77" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F77" t="s">
+        <v>30</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" t="s">
+        <v>41</v>
+      </c>
+      <c r="J77" s="2">
+        <v>46342.791666666664</v>
+      </c>
+      <c r="K77" s="2">
+        <v>46343.75</v>
+      </c>
+      <c r="L77" t="s">
         <v>42</v>
-      </c>
-      <c r="I77" t="s">
-        <v>19</v>
-      </c>
-      <c r="J77" s="2">
-        <v>46342.25</v>
-      </c>
-      <c r="K77" s="2">
-        <v>46344.25</v>
-      </c>
-      <c r="L77" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3720,34 +3723,31 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C78" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D78" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F78" t="s">
-        <v>38</v>
-      </c>
-      <c r="G78" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="I78" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J78" s="2">
-        <v>46342.791666666664</v>
+        <v>46343.208333333336</v>
       </c>
       <c r="K78" s="2">
-        <v>46343.75</v>
+        <v>46345.125</v>
       </c>
       <c r="L78" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3755,31 +3755,34 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C79" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D79" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F79" t="s">
-        <v>126</v>
+        <v>30</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J79" s="2">
-        <v>46343.208333333336</v>
+        <v>46343.25</v>
       </c>
       <c r="K79" s="2">
-        <v>46345.125</v>
+        <v>46343.75</v>
       </c>
       <c r="L79" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3787,25 +3790,28 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="C80" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D80" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F80" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="G80" t="s">
         <v>18</v>
       </c>
+      <c r="H80" t="s">
+        <v>25</v>
+      </c>
       <c r="I80" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J80" s="2">
         <v>46343.25</v>
@@ -3814,7 +3820,7 @@
         <v>46343.75</v>
       </c>
       <c r="L80" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3822,28 +3828,25 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C81" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D81" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F81" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="G81" t="s">
         <v>18</v>
       </c>
-      <c r="H81" t="s">
-        <v>25</v>
-      </c>
       <c r="I81" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J81" s="2">
         <v>46343.25</v>
@@ -3852,7 +3855,7 @@
         <v>46343.75</v>
       </c>
       <c r="L81" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3860,34 +3863,31 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F82" t="s">
-        <v>38</v>
-      </c>
-      <c r="G82" t="s">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="I82" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J82" s="2">
-        <v>46343.25</v>
+        <v>46343.3125</v>
       </c>
       <c r="K82" s="2">
-        <v>46343.75</v>
+        <v>46346.604166666664</v>
       </c>
       <c r="L82" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3895,31 +3895,34 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D83" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F83" t="s">
-        <v>186</v>
+        <v>30</v>
+      </c>
+      <c r="G83" t="s">
+        <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="J83" s="2">
-        <v>46343.3125</v>
+        <v>46343.791666666664</v>
       </c>
       <c r="K83" s="2">
-        <v>46346.604166666664</v>
+        <v>46344.75</v>
       </c>
       <c r="L83" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3927,10 +3930,10 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C84" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D84" t="s">
         <v>182</v>
@@ -3939,13 +3942,13 @@
         <v>183</v>
       </c>
       <c r="F84" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="G84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J84" s="2">
         <v>46343.791666666664</v>
@@ -3954,7 +3957,7 @@
         <v>46344.75</v>
       </c>
       <c r="L84" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -3962,92 +3965,86 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C85" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D85" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="F85" t="s">
-        <v>89</v>
-      </c>
-      <c r="G85" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I85" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J85" s="2">
-        <v>46343.791666666664</v>
+        <v>46344</v>
       </c>
       <c r="K85" s="2">
-        <v>46344.75</v>
+        <v>46346</v>
       </c>
       <c r="L85" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>39</v>
-      </c>
-      <c r="C86" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="D86" t="s">
-        <v>187</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F86" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="I86" t="s">
         <v>19</v>
       </c>
       <c r="J86" s="2">
-        <v>46344</v>
+        <v>46344.083333333336</v>
       </c>
       <c r="K86" s="2">
-        <v>46346</v>
+        <v>46345.208333333336</v>
       </c>
       <c r="L86" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>51</v>
+        <v>21</v>
+      </c>
+      <c r="C87" t="s">
+        <v>78</v>
       </c>
       <c r="D87" t="s">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="F87" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
       </c>
       <c r="J87" s="2">
-        <v>46344.083333333336</v>
+        <v>46344.291666666664</v>
       </c>
       <c r="K87" s="2">
-        <v>46345.208333333336</v>
+        <v>46344.791666666664</v>
       </c>
       <c r="L87" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4055,28 +4052,34 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D88" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="F88" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="G88" t="s">
+        <v>90</v>
+      </c>
+      <c r="H88" t="s">
+        <v>90</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="J88" s="2">
-        <v>46344.291666666664</v>
+        <v>46344.625</v>
       </c>
       <c r="K88" s="2">
-        <v>46344.791666666664</v>
+        <v>46345.041666666664</v>
       </c>
       <c r="L88" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4084,173 +4087,170 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C89" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="D89" t="s">
-        <v>99</v>
+        <v>190</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="F89" t="s">
         <v>30</v>
       </c>
       <c r="G89" t="s">
-        <v>31</v>
-      </c>
-      <c r="H89" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J89" s="2">
-        <v>46344.625</v>
+        <v>46345.25</v>
       </c>
       <c r="K89" s="2">
-        <v>46345.041666666664</v>
+        <v>46345.75</v>
       </c>
       <c r="L89" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B90" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C90" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D90" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F90" t="s">
-        <v>38</v>
-      </c>
-      <c r="G90" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="I90" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J90" s="2">
-        <v>46345.25</v>
+        <v>46345.291666666664</v>
       </c>
       <c r="K90" s="2">
-        <v>46345.75</v>
+        <v>46346.166666666664</v>
       </c>
       <c r="L90" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B91" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="C91" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D91" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F91" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="I91" t="s">
         <v>19</v>
       </c>
       <c r="J91" s="2">
-        <v>46345.291666666664</v>
+        <v>46346.23333333333</v>
       </c>
       <c r="K91" s="2">
-        <v>46346.166666666664</v>
+        <v>46347.275000000001</v>
       </c>
       <c r="L91" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C92" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>194</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="F92" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="I92" t="s">
         <v>19</v>
       </c>
       <c r="J92" s="2">
-        <v>46346.23333333333</v>
+        <v>46346.333333333336</v>
       </c>
       <c r="K92" s="2">
-        <v>46347.275000000001</v>
+        <v>46346.833333333336</v>
       </c>
       <c r="L92" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C93" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D93" t="s">
-        <v>151</v>
+        <v>196</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="F93" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
       </c>
       <c r="J93" s="2">
-        <v>46346.333333333336</v>
+        <v>46346.395833333336</v>
       </c>
       <c r="K93" s="2">
-        <v>46346.833333333336</v>
+        <v>46347.604166666664</v>
       </c>
       <c r="L93" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B94" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C94" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D94" t="s">
         <v>196</v>
@@ -4271,47 +4271,47 @@
         <v>46347.604166666664</v>
       </c>
       <c r="L94" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B95" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C95" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="D95" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F95" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="I95" t="s">
         <v>19</v>
       </c>
       <c r="J95" s="2">
-        <v>46346.395833333336</v>
+        <v>46346.583333333336</v>
       </c>
       <c r="K95" s="2">
-        <v>46347.604166666664</v>
+        <v>46348.083333333336</v>
       </c>
       <c r="L95" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B96" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C96" t="s">
         <v>198</v>
@@ -4335,74 +4335,42 @@
         <v>46348.083333333336</v>
       </c>
       <c r="L96" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="C97" t="s">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="D97" t="s">
-        <v>199</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>200</v>
+        <v>119</v>
       </c>
       <c r="F97" t="s">
-        <v>186</v>
+        <v>89</v>
+      </c>
+      <c r="G97" t="s">
+        <v>90</v>
+      </c>
+      <c r="H97" t="s">
+        <v>90</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="J97" s="2">
-        <v>46346.583333333336</v>
+        <v>46346.625</v>
       </c>
       <c r="K97" s="2">
-        <v>46348.083333333336</v>
+        <v>46347.041666666664</v>
       </c>
       <c r="L97" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12">
-      <c r="A98" t="s">
-        <v>12</v>
-      </c>
-      <c r="B98" t="s">
-        <v>27</v>
-      </c>
-      <c r="C98" t="s">
-        <v>28</v>
-      </c>
-      <c r="D98" t="s">
-        <v>29</v>
-      </c>
-      <c r="F98" t="s">
-        <v>30</v>
-      </c>
-      <c r="G98" t="s">
-        <v>31</v>
-      </c>
-      <c r="H98" t="s">
-        <v>31</v>
-      </c>
-      <c r="I98" t="s">
-        <v>32</v>
-      </c>
-      <c r="J98" s="2">
-        <v>46346.625</v>
-      </c>
-      <c r="K98" s="2">
-        <v>46347.041666666664</v>
-      </c>
-      <c r="L98" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
